--- a/Produtos.xlsx
+++ b/Produtos.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\NOT-MARCOS\Documents\GitHub\Catalogo-Olympikus\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{510CEE63-69D3-43FD-96B2-647E2E182B88}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B5862FA0-CE44-4CFA-8572-6776E94EDCF1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{C851EA1D-5267-41B7-9513-D07E5A57DEF2}"/>
   </bookViews>

--- a/Produtos.xlsx
+++ b/Produtos.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\NOT-MARCOS\Documents\GitHub\Catalogo-Olympikus\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B5862FA0-CE44-4CFA-8572-6776E94EDCF1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{915A54ED-4A28-472C-9EFC-6189A588E865}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{C851EA1D-5267-41B7-9513-D07E5A57DEF2}"/>
   </bookViews>
@@ -4738,7 +4738,6 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E0D1E054-7418-4233-9A16-A15E844DE850}">
-  <sheetPr filterMode="1"/>
   <dimension ref="A1:M808"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -4780,7 +4779,7 @@
         <v>587</v>
       </c>
     </row>
-    <row r="2" spans="1:13" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:13" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>827</v>
       </c>
@@ -4812,7 +4811,7 @@
         <v>139.995</v>
       </c>
     </row>
-    <row r="3" spans="1:13" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:13" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
         <v>828</v>
       </c>
@@ -4844,7 +4843,7 @@
         <v>139.995</v>
       </c>
     </row>
-    <row r="4" spans="1:13" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:13" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
         <v>611</v>
       </c>
@@ -4876,7 +4875,7 @@
         <v>139.995</v>
       </c>
     </row>
-    <row r="5" spans="1:13" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:13" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
         <v>612</v>
       </c>
@@ -4909,7 +4908,7 @@
       </c>
       <c r="M5" s="5"/>
     </row>
-    <row r="6" spans="1:13" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:13" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
         <v>613</v>
       </c>
@@ -4941,7 +4940,7 @@
         <v>139.995</v>
       </c>
     </row>
-    <row r="7" spans="1:13" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:13" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
         <v>614</v>
       </c>
@@ -4973,7 +4972,7 @@
         <v>139.995</v>
       </c>
     </row>
-    <row r="8" spans="1:13" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:13" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
         <v>615</v>
       </c>
@@ -5005,7 +5004,7 @@
         <v>114.995</v>
       </c>
     </row>
-    <row r="9" spans="1:13" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:13" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
         <v>616</v>
       </c>
@@ -5037,7 +5036,7 @@
         <v>114.995</v>
       </c>
     </row>
-    <row r="10" spans="1:13" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:13" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
         <v>617</v>
       </c>
@@ -5069,7 +5068,7 @@
         <v>114.995</v>
       </c>
     </row>
-    <row r="11" spans="1:13" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:13" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
         <v>618</v>
       </c>
@@ -5101,7 +5100,7 @@
         <v>114.995</v>
       </c>
     </row>
-    <row r="12" spans="1:13" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:13" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
         <v>619</v>
       </c>
@@ -5133,7 +5132,7 @@
         <v>149.995</v>
       </c>
     </row>
-    <row r="13" spans="1:13" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:13" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
         <v>620</v>
       </c>
@@ -5165,7 +5164,7 @@
         <v>149.995</v>
       </c>
     </row>
-    <row r="14" spans="1:13" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:13" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
         <v>621</v>
       </c>
@@ -5197,7 +5196,7 @@
         <v>149.995</v>
       </c>
     </row>
-    <row r="15" spans="1:13" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:13" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
         <v>622</v>
       </c>
@@ -5229,7 +5228,7 @@
         <v>149.995</v>
       </c>
     </row>
-    <row r="16" spans="1:13" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:13" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
         <v>623</v>
       </c>
@@ -5261,7 +5260,7 @@
         <v>149.995</v>
       </c>
     </row>
-    <row r="17" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
         <v>829</v>
       </c>
@@ -5293,7 +5292,7 @@
         <v>149.995</v>
       </c>
     </row>
-    <row r="18" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
         <v>624</v>
       </c>
@@ -5325,7 +5324,7 @@
         <v>149.995</v>
       </c>
     </row>
-    <row r="19" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
         <v>625</v>
       </c>
@@ -5357,7 +5356,7 @@
         <v>149.995</v>
       </c>
     </row>
-    <row r="20" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
         <v>626</v>
       </c>
@@ -5389,7 +5388,7 @@
         <v>149.995</v>
       </c>
     </row>
-    <row r="21" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
         <v>1387</v>
       </c>
@@ -5421,7 +5420,7 @@
         <v>129.995</v>
       </c>
     </row>
-    <row r="22" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
         <v>1388</v>
       </c>
@@ -5453,7 +5452,7 @@
         <v>129.995</v>
       </c>
     </row>
-    <row r="23" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
         <v>1389</v>
       </c>
@@ -5485,7 +5484,7 @@
         <v>129.995</v>
       </c>
     </row>
-    <row r="24" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
         <v>1386</v>
       </c>
@@ -5517,7 +5516,7 @@
         <v>129.995</v>
       </c>
     </row>
-    <row r="25" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
         <v>830</v>
       </c>
@@ -5549,7 +5548,7 @@
         <v>139.995</v>
       </c>
     </row>
-    <row r="26" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
         <v>627</v>
       </c>
@@ -5581,7 +5580,7 @@
         <v>139.995</v>
       </c>
     </row>
-    <row r="27" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
         <v>628</v>
       </c>
@@ -5613,7 +5612,7 @@
         <v>139.995</v>
       </c>
     </row>
-    <row r="28" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
         <v>629</v>
       </c>
@@ -5645,7 +5644,7 @@
         <v>139.995</v>
       </c>
     </row>
-    <row r="29" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="2" t="s">
         <v>831</v>
       </c>
@@ -5677,7 +5676,7 @@
         <v>129.995</v>
       </c>
     </row>
-    <row r="30" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="2" t="s">
         <v>832</v>
       </c>
@@ -5709,7 +5708,7 @@
         <v>129.995</v>
       </c>
     </row>
-    <row r="31" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="2" t="s">
         <v>833</v>
       </c>
@@ -5741,7 +5740,7 @@
         <v>129.995</v>
       </c>
     </row>
-    <row r="32" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="2" t="s">
         <v>630</v>
       </c>
@@ -5773,7 +5772,7 @@
         <v>129.995</v>
       </c>
     </row>
-    <row r="33" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="2" t="s">
         <v>631</v>
       </c>
@@ -5805,7 +5804,7 @@
         <v>124.995</v>
       </c>
     </row>
-    <row r="34" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="2" t="s">
         <v>632</v>
       </c>
@@ -5837,7 +5836,7 @@
         <v>124.995</v>
       </c>
     </row>
-    <row r="35" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="2" t="s">
         <v>633</v>
       </c>
@@ -5869,7 +5868,7 @@
         <v>124.995</v>
       </c>
     </row>
-    <row r="36" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="2" t="s">
         <v>834</v>
       </c>
@@ -5901,7 +5900,7 @@
         <v>129.995</v>
       </c>
     </row>
-    <row r="37" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="2" t="s">
         <v>634</v>
       </c>
@@ -5933,7 +5932,7 @@
         <v>129.995</v>
       </c>
     </row>
-    <row r="38" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="2" t="s">
         <v>835</v>
       </c>
@@ -5965,7 +5964,7 @@
         <v>129.995</v>
       </c>
     </row>
-    <row r="39" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="2" t="s">
         <v>635</v>
       </c>
@@ -5997,7 +5996,7 @@
         <v>129.995</v>
       </c>
     </row>
-    <row r="40" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="2" t="s">
         <v>636</v>
       </c>
@@ -6029,7 +6028,7 @@
         <v>129.995</v>
       </c>
     </row>
-    <row r="41" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="2" t="s">
         <v>836</v>
       </c>
@@ -6061,7 +6060,7 @@
         <v>124.995</v>
       </c>
     </row>
-    <row r="42" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="2" t="s">
         <v>837</v>
       </c>
@@ -6093,7 +6092,7 @@
         <v>124.995</v>
       </c>
     </row>
-    <row r="43" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="2" t="s">
         <v>637</v>
       </c>
@@ -6125,7 +6124,7 @@
         <v>124.995</v>
       </c>
     </row>
-    <row r="44" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="2" t="s">
         <v>638</v>
       </c>
@@ -6157,7 +6156,7 @@
         <v>114.995</v>
       </c>
     </row>
-    <row r="45" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="2" t="s">
         <v>838</v>
       </c>
@@ -6189,7 +6188,7 @@
         <v>114.995</v>
       </c>
     </row>
-    <row r="46" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" s="2" t="s">
         <v>639</v>
       </c>
@@ -6221,7 +6220,7 @@
         <v>114.995</v>
       </c>
     </row>
-    <row r="47" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="2" t="s">
         <v>640</v>
       </c>
@@ -6253,7 +6252,7 @@
         <v>99.995000000000005</v>
       </c>
     </row>
-    <row r="48" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="2" t="s">
         <v>839</v>
       </c>
@@ -6285,7 +6284,7 @@
         <v>99.995000000000005</v>
       </c>
     </row>
-    <row r="49" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" s="2" t="s">
         <v>641</v>
       </c>
@@ -6317,7 +6316,7 @@
         <v>99.995000000000005</v>
       </c>
     </row>
-    <row r="50" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50" s="2" t="s">
         <v>840</v>
       </c>
@@ -6349,7 +6348,7 @@
         <v>99.995000000000005</v>
       </c>
     </row>
-    <row r="51" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A51" s="2" t="s">
         <v>642</v>
       </c>
@@ -6381,7 +6380,7 @@
         <v>99.995000000000005</v>
       </c>
     </row>
-    <row r="52" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A52" s="2" t="s">
         <v>841</v>
       </c>
@@ -6413,7 +6412,7 @@
         <v>114.995</v>
       </c>
     </row>
-    <row r="53" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A53" s="2" t="s">
         <v>643</v>
       </c>
@@ -6445,7 +6444,7 @@
         <v>114.995</v>
       </c>
     </row>
-    <row r="54" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A54" s="2" t="s">
         <v>644</v>
       </c>
@@ -6477,7 +6476,7 @@
         <v>114.995</v>
       </c>
     </row>
-    <row r="55" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A55" s="2" t="s">
         <v>645</v>
       </c>
@@ -6509,7 +6508,7 @@
         <v>114.995</v>
       </c>
     </row>
-    <row r="56" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A56" s="2" t="s">
         <v>842</v>
       </c>
@@ -6541,7 +6540,7 @@
         <v>124.995</v>
       </c>
     </row>
-    <row r="57" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A57" s="2" t="s">
         <v>646</v>
       </c>
@@ -6573,7 +6572,7 @@
         <v>124.995</v>
       </c>
     </row>
-    <row r="58" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A58" s="2" t="s">
         <v>647</v>
       </c>
@@ -6605,7 +6604,7 @@
         <v>124.995</v>
       </c>
     </row>
-    <row r="59" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A59" s="2" t="s">
         <v>648</v>
       </c>
@@ -6637,7 +6636,7 @@
         <v>124.995</v>
       </c>
     </row>
-    <row r="60" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A60" s="2" t="s">
         <v>649</v>
       </c>
@@ -6669,7 +6668,7 @@
         <v>124.995</v>
       </c>
     </row>
-    <row r="61" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A61" s="2" t="s">
         <v>843</v>
       </c>
@@ -6701,7 +6700,7 @@
         <v>99.995000000000005</v>
       </c>
     </row>
-    <row r="62" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A62" s="2" t="s">
         <v>650</v>
       </c>
@@ -6733,7 +6732,7 @@
         <v>99.995000000000005</v>
       </c>
     </row>
-    <row r="63" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A63" s="2" t="s">
         <v>651</v>
       </c>
@@ -6765,7 +6764,7 @@
         <v>99.995000000000005</v>
       </c>
     </row>
-    <row r="64" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A64" s="2" t="s">
         <v>652</v>
       </c>
@@ -6797,7 +6796,7 @@
         <v>99.995000000000005</v>
       </c>
     </row>
-    <row r="65" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A65" s="2" t="s">
         <v>844</v>
       </c>
@@ -6829,7 +6828,7 @@
         <v>99.995000000000005</v>
       </c>
     </row>
-    <row r="66" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A66" s="2" t="s">
         <v>845</v>
       </c>
@@ -6861,7 +6860,7 @@
         <v>99.995000000000005</v>
       </c>
     </row>
-    <row r="67" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A67" s="2" t="s">
         <v>653</v>
       </c>
@@ -6893,7 +6892,7 @@
         <v>99.995000000000005</v>
       </c>
     </row>
-    <row r="68" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A68" s="2" t="s">
         <v>654</v>
       </c>
@@ -6925,7 +6924,7 @@
         <v>99.995000000000005</v>
       </c>
     </row>
-    <row r="69" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A69" s="2" t="s">
         <v>655</v>
       </c>
@@ -6957,7 +6956,7 @@
         <v>99.995000000000005</v>
       </c>
     </row>
-    <row r="70" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A70" s="2" t="s">
         <v>656</v>
       </c>
@@ -6989,7 +6988,7 @@
         <v>99.995000000000005</v>
       </c>
     </row>
-    <row r="71" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A71" s="2" t="s">
         <v>1394</v>
       </c>
@@ -7021,7 +7020,7 @@
         <v>99.995000000000005</v>
       </c>
     </row>
-    <row r="72" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A72" s="2" t="s">
         <v>1395</v>
       </c>
@@ -7053,7 +7052,7 @@
         <v>99.995000000000005</v>
       </c>
     </row>
-    <row r="73" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A73" s="2" t="s">
         <v>1396</v>
       </c>
@@ -7085,7 +7084,7 @@
         <v>99.995000000000005</v>
       </c>
     </row>
-    <row r="74" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A74" s="2" t="s">
         <v>1397</v>
       </c>
@@ -7117,7 +7116,7 @@
         <v>99.995000000000005</v>
       </c>
     </row>
-    <row r="75" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A75" s="2" t="s">
         <v>657</v>
       </c>
@@ -7149,7 +7148,7 @@
         <v>139.995</v>
       </c>
     </row>
-    <row r="76" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A76" s="2" t="s">
         <v>658</v>
       </c>
@@ -7181,7 +7180,7 @@
         <v>139.995</v>
       </c>
     </row>
-    <row r="77" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A77" s="2" t="s">
         <v>659</v>
       </c>
@@ -7213,7 +7212,7 @@
         <v>139.995</v>
       </c>
     </row>
-    <row r="78" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A78" s="2" t="s">
         <v>660</v>
       </c>
@@ -7245,7 +7244,7 @@
         <v>129.995</v>
       </c>
     </row>
-    <row r="79" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A79" s="2" t="s">
         <v>846</v>
       </c>
@@ -7277,7 +7276,7 @@
         <v>129.995</v>
       </c>
     </row>
-    <row r="80" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A80" s="2" t="s">
         <v>661</v>
       </c>
@@ -7309,7 +7308,7 @@
         <v>129.995</v>
       </c>
     </row>
-    <row r="81" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A81" s="2" t="s">
         <v>662</v>
       </c>
@@ -7341,7 +7340,7 @@
         <v>129.995</v>
       </c>
     </row>
-    <row r="82" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A82" s="2" t="s">
         <v>847</v>
       </c>
@@ -7373,7 +7372,7 @@
         <v>124.995</v>
       </c>
     </row>
-    <row r="83" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A83" s="2" t="s">
         <v>663</v>
       </c>
@@ -7405,7 +7404,7 @@
         <v>124.995</v>
       </c>
     </row>
-    <row r="84" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A84" s="2" t="s">
         <v>664</v>
       </c>
@@ -7437,7 +7436,7 @@
         <v>124.995</v>
       </c>
     </row>
-    <row r="85" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A85" s="2" t="s">
         <v>665</v>
       </c>
@@ -7469,7 +7468,7 @@
         <v>124.995</v>
       </c>
     </row>
-    <row r="86" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A86" s="2" t="s">
         <v>666</v>
       </c>
@@ -7501,7 +7500,7 @@
         <v>124.995</v>
       </c>
     </row>
-    <row r="87" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A87" s="2" t="s">
         <v>667</v>
       </c>
@@ -7533,7 +7532,7 @@
         <v>124.995</v>
       </c>
     </row>
-    <row r="88" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A88" s="2" t="s">
         <v>668</v>
       </c>
@@ -7565,7 +7564,7 @@
         <v>124.995</v>
       </c>
     </row>
-    <row r="89" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A89" s="2" t="s">
         <v>669</v>
       </c>
@@ -7597,7 +7596,7 @@
         <v>124.995</v>
       </c>
     </row>
-    <row r="90" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A90" s="2" t="s">
         <v>670</v>
       </c>
@@ -7629,7 +7628,7 @@
         <v>124.995</v>
       </c>
     </row>
-    <row r="91" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A91" s="2" t="s">
         <v>671</v>
       </c>
@@ -7661,7 +7660,7 @@
         <v>124.995</v>
       </c>
     </row>
-    <row r="92" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A92" s="2" t="s">
         <v>848</v>
       </c>
@@ -7693,7 +7692,7 @@
         <v>124.995</v>
       </c>
     </row>
-    <row r="93" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A93" s="2" t="s">
         <v>672</v>
       </c>
@@ -7725,7 +7724,7 @@
         <v>114.995</v>
       </c>
     </row>
-    <row r="94" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A94" s="2" t="s">
         <v>673</v>
       </c>
@@ -7757,7 +7756,7 @@
         <v>114.995</v>
       </c>
     </row>
-    <row r="95" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A95" s="2" t="s">
         <v>674</v>
       </c>
@@ -7789,7 +7788,7 @@
         <v>114.995</v>
       </c>
     </row>
-    <row r="96" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A96" s="2" t="s">
         <v>675</v>
       </c>
@@ -7821,7 +7820,7 @@
         <v>114.995</v>
       </c>
     </row>
-    <row r="97" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A97" s="2" t="s">
         <v>676</v>
       </c>
@@ -7853,7 +7852,7 @@
         <v>114.995</v>
       </c>
     </row>
-    <row r="98" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A98" s="2" t="s">
         <v>677</v>
       </c>
@@ -7885,7 +7884,7 @@
         <v>114.995</v>
       </c>
     </row>
-    <row r="99" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A99" s="2" t="s">
         <v>678</v>
       </c>
@@ -7917,7 +7916,7 @@
         <v>114.995</v>
       </c>
     </row>
-    <row r="100" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A100" s="2" t="s">
         <v>679</v>
       </c>
@@ -7949,7 +7948,7 @@
         <v>114.995</v>
       </c>
     </row>
-    <row r="101" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A101" s="2" t="s">
         <v>680</v>
       </c>
@@ -7981,7 +7980,7 @@
         <v>114.995</v>
       </c>
     </row>
-    <row r="102" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A102" s="2" t="s">
         <v>849</v>
       </c>
@@ -8013,7 +8012,7 @@
         <v>114.995</v>
       </c>
     </row>
-    <row r="103" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A103" s="2" t="s">
         <v>681</v>
       </c>
@@ -8045,7 +8044,7 @@
         <v>114.995</v>
       </c>
     </row>
-    <row r="104" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A104" s="2" t="s">
         <v>682</v>
       </c>
@@ -8077,7 +8076,7 @@
         <v>114.995</v>
       </c>
     </row>
-    <row r="105" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A105" s="2" t="s">
         <v>683</v>
       </c>
@@ -8109,7 +8108,7 @@
         <v>114.995</v>
       </c>
     </row>
-    <row r="106" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A106" s="2" t="s">
         <v>684</v>
       </c>
@@ -8141,7 +8140,7 @@
         <v>114.995</v>
       </c>
     </row>
-    <row r="107" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A107" s="2" t="s">
         <v>685</v>
       </c>
@@ -8173,7 +8172,7 @@
         <v>114.995</v>
       </c>
     </row>
-    <row r="108" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A108" s="2" t="s">
         <v>686</v>
       </c>
@@ -8205,7 +8204,7 @@
         <v>114.995</v>
       </c>
     </row>
-    <row r="109" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A109" s="2" t="s">
         <v>687</v>
       </c>
@@ -8237,7 +8236,7 @@
         <v>114.995</v>
       </c>
     </row>
-    <row r="110" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A110" s="2" t="s">
         <v>688</v>
       </c>
@@ -8269,7 +8268,7 @@
         <v>114.995</v>
       </c>
     </row>
-    <row r="111" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A111" s="2" t="s">
         <v>689</v>
       </c>
@@ -8301,7 +8300,7 @@
         <v>114.995</v>
       </c>
     </row>
-    <row r="112" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A112" s="2" t="s">
         <v>690</v>
       </c>
@@ -8333,7 +8332,7 @@
         <v>114.995</v>
       </c>
     </row>
-    <row r="113" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A113" s="2" t="s">
         <v>691</v>
       </c>
@@ -8365,7 +8364,7 @@
         <v>114.995</v>
       </c>
     </row>
-    <row r="114" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A114" s="2" t="s">
         <v>692</v>
       </c>
@@ -8397,7 +8396,7 @@
         <v>94.995000000000005</v>
       </c>
     </row>
-    <row r="115" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A115" s="2" t="s">
         <v>850</v>
       </c>
@@ -8429,7 +8428,7 @@
         <v>94.995000000000005</v>
       </c>
     </row>
-    <row r="116" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A116" s="2" t="s">
         <v>693</v>
       </c>
@@ -8461,7 +8460,7 @@
         <v>94.995000000000005</v>
       </c>
     </row>
-    <row r="117" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A117" s="2" t="s">
         <v>694</v>
       </c>
@@ -8493,7 +8492,7 @@
         <v>94.995000000000005</v>
       </c>
     </row>
-    <row r="118" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A118" s="2" t="s">
         <v>1399</v>
       </c>
@@ -8525,7 +8524,7 @@
         <v>99.995000000000005</v>
       </c>
     </row>
-    <row r="119" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A119" s="2" t="s">
         <v>1400</v>
       </c>
@@ -8557,7 +8556,7 @@
         <v>99.995000000000005</v>
       </c>
     </row>
-    <row r="120" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A120" s="2" t="s">
         <v>1401</v>
       </c>
@@ -8589,7 +8588,7 @@
         <v>99.995000000000005</v>
       </c>
     </row>
-    <row r="121" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A121" s="2" t="s">
         <v>695</v>
       </c>
@@ -8621,7 +8620,7 @@
         <v>94.995000000000005</v>
       </c>
     </row>
-    <row r="122" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A122" s="2" t="s">
         <v>851</v>
       </c>
@@ -8653,7 +8652,7 @@
         <v>94.995000000000005</v>
       </c>
     </row>
-    <row r="123" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A123" s="2" t="s">
         <v>696</v>
       </c>
@@ -8685,7 +8684,7 @@
         <v>94.995000000000005</v>
       </c>
     </row>
-    <row r="124" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A124" s="2" t="s">
         <v>697</v>
       </c>
@@ -8717,7 +8716,7 @@
         <v>94.995000000000005</v>
       </c>
     </row>
-    <row r="125" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A125" s="2" t="s">
         <v>698</v>
       </c>
@@ -8749,7 +8748,7 @@
         <v>99.995000000000005</v>
       </c>
     </row>
-    <row r="126" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A126" s="2" t="s">
         <v>699</v>
       </c>
@@ -8781,7 +8780,7 @@
         <v>99.995000000000005</v>
       </c>
     </row>
-    <row r="127" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A127" s="2" t="s">
         <v>700</v>
       </c>
@@ -8813,7 +8812,7 @@
         <v>99.995000000000005</v>
       </c>
     </row>
-    <row r="128" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A128" s="2" t="s">
         <v>701</v>
       </c>
@@ -8845,7 +8844,7 @@
         <v>94.995000000000005</v>
       </c>
     </row>
-    <row r="129" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A129" s="2" t="s">
         <v>702</v>
       </c>
@@ -8877,7 +8876,7 @@
         <v>94.995000000000005</v>
       </c>
     </row>
-    <row r="130" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A130" s="2" t="s">
         <v>703</v>
       </c>
@@ -8909,7 +8908,7 @@
         <v>94.995000000000005</v>
       </c>
     </row>
-    <row r="131" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A131" s="2" t="s">
         <v>704</v>
       </c>
@@ -8941,7 +8940,7 @@
         <v>149.995</v>
       </c>
     </row>
-    <row r="132" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A132" s="2" t="s">
         <v>852</v>
       </c>
@@ -8973,7 +8972,7 @@
         <v>149.995</v>
       </c>
     </row>
-    <row r="133" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A133" s="2" t="s">
         <v>705</v>
       </c>
@@ -9005,7 +9004,7 @@
         <v>149.995</v>
       </c>
     </row>
-    <row r="134" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A134" s="2" t="s">
         <v>853</v>
       </c>
@@ -9037,7 +9036,7 @@
         <v>149.995</v>
       </c>
     </row>
-    <row r="135" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A135" s="2" t="s">
         <v>854</v>
       </c>
@@ -9069,7 +9068,7 @@
         <v>149.995</v>
       </c>
     </row>
-    <row r="136" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A136" s="2" t="s">
         <v>706</v>
       </c>
@@ -9101,7 +9100,7 @@
         <v>149.995</v>
       </c>
     </row>
-    <row r="137" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A137" s="2" t="s">
         <v>855</v>
       </c>
@@ -9133,7 +9132,7 @@
         <v>149.995</v>
       </c>
     </row>
-    <row r="138" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A138" s="2" t="s">
         <v>707</v>
       </c>
@@ -9165,7 +9164,7 @@
         <v>149.995</v>
       </c>
     </row>
-    <row r="139" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A139" s="2" t="s">
         <v>856</v>
       </c>
@@ -9197,7 +9196,7 @@
         <v>149.995</v>
       </c>
     </row>
-    <row r="140" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A140" s="2" t="s">
         <v>708</v>
       </c>
@@ -9229,7 +9228,7 @@
         <v>149.995</v>
       </c>
     </row>
-    <row r="141" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A141" s="2" t="s">
         <v>857</v>
       </c>
@@ -9261,7 +9260,7 @@
         <v>139.995</v>
       </c>
     </row>
-    <row r="142" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A142" s="2" t="s">
         <v>709</v>
       </c>
@@ -9293,7 +9292,7 @@
         <v>139.995</v>
       </c>
     </row>
-    <row r="143" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A143" s="2" t="s">
         <v>710</v>
       </c>
@@ -9325,7 +9324,7 @@
         <v>139.995</v>
       </c>
     </row>
-    <row r="144" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A144" s="2" t="s">
         <v>711</v>
       </c>
@@ -9357,7 +9356,7 @@
         <v>139.995</v>
       </c>
     </row>
-    <row r="145" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A145" s="2" t="s">
         <v>712</v>
       </c>
@@ -9389,7 +9388,7 @@
         <v>139.995</v>
       </c>
     </row>
-    <row r="146" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A146" s="2" t="s">
         <v>713</v>
       </c>
@@ -9421,7 +9420,7 @@
         <v>114.995</v>
       </c>
     </row>
-    <row r="147" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A147" s="2" t="s">
         <v>858</v>
       </c>
@@ -9453,7 +9452,7 @@
         <v>114.995</v>
       </c>
     </row>
-    <row r="148" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A148" s="2" t="s">
         <v>714</v>
       </c>
@@ -9485,7 +9484,7 @@
         <v>114.995</v>
       </c>
     </row>
-    <row r="149" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A149" s="2" t="s">
         <v>859</v>
       </c>
@@ -9517,7 +9516,7 @@
         <v>114.995</v>
       </c>
     </row>
-    <row r="150" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A150" s="2" t="s">
         <v>860</v>
       </c>
@@ -9549,7 +9548,7 @@
         <v>99.995000000000005</v>
       </c>
     </row>
-    <row r="151" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A151" s="2" t="s">
         <v>715</v>
       </c>
@@ -9581,7 +9580,7 @@
         <v>99.995000000000005</v>
       </c>
     </row>
-    <row r="152" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A152" s="2" t="s">
         <v>716</v>
       </c>
@@ -9613,7 +9612,7 @@
         <v>99.995000000000005</v>
       </c>
     </row>
-    <row r="153" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A153" s="2" t="s">
         <v>717</v>
       </c>
@@ -9645,7 +9644,7 @@
         <v>114.995</v>
       </c>
     </row>
-    <row r="154" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A154" s="2" t="s">
         <v>861</v>
       </c>
@@ -9677,7 +9676,7 @@
         <v>114.995</v>
       </c>
     </row>
-    <row r="155" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A155" s="2" t="s">
         <v>718</v>
       </c>
@@ -9709,7 +9708,7 @@
         <v>114.995</v>
       </c>
     </row>
-    <row r="156" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A156" s="2" t="s">
         <v>719</v>
       </c>
@@ -9741,7 +9740,7 @@
         <v>114.995</v>
       </c>
     </row>
-    <row r="157" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A157" s="2" t="s">
         <v>862</v>
       </c>
@@ -9773,7 +9772,7 @@
         <v>124.995</v>
       </c>
     </row>
-    <row r="158" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A158" s="2" t="s">
         <v>720</v>
       </c>
@@ -9805,7 +9804,7 @@
         <v>124.995</v>
       </c>
     </row>
-    <row r="159" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A159" s="2" t="s">
         <v>721</v>
       </c>
@@ -9837,7 +9836,7 @@
         <v>124.995</v>
       </c>
     </row>
-    <row r="160" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A160" s="2" t="s">
         <v>722</v>
       </c>
@@ -9869,7 +9868,7 @@
         <v>124.995</v>
       </c>
     </row>
-    <row r="161" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A161" s="2" t="s">
         <v>863</v>
       </c>
@@ -9901,7 +9900,7 @@
         <v>99.995000000000005</v>
       </c>
     </row>
-    <row r="162" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A162" s="2" t="s">
         <v>723</v>
       </c>
@@ -9933,7 +9932,7 @@
         <v>99.995000000000005</v>
       </c>
     </row>
-    <row r="163" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A163" s="2" t="s">
         <v>724</v>
       </c>
@@ -9965,7 +9964,7 @@
         <v>99.995000000000005</v>
       </c>
     </row>
-    <row r="164" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A164" s="2" t="s">
         <v>725</v>
       </c>
@@ -9997,7 +9996,7 @@
         <v>99.995000000000005</v>
       </c>
     </row>
-    <row r="165" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A165" s="2" t="s">
         <v>864</v>
       </c>
@@ -10029,7 +10028,7 @@
         <v>99.995000000000005</v>
       </c>
     </row>
-    <row r="166" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A166" s="2" t="s">
         <v>726</v>
       </c>
@@ -10061,7 +10060,7 @@
         <v>94.995000000000005</v>
       </c>
     </row>
-    <row r="167" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A167" s="2" t="s">
         <v>727</v>
       </c>
@@ -10093,7 +10092,7 @@
         <v>94.995000000000005</v>
       </c>
     </row>
-    <row r="168" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A168" s="2" t="s">
         <v>728</v>
       </c>
@@ -10125,7 +10124,7 @@
         <v>94.995000000000005</v>
       </c>
     </row>
-    <row r="169" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A169" s="2" t="s">
         <v>729</v>
       </c>
@@ -10157,7 +10156,7 @@
         <v>114.995</v>
       </c>
     </row>
-    <row r="170" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A170" s="2" t="s">
         <v>865</v>
       </c>
@@ -10189,7 +10188,7 @@
         <v>114.995</v>
       </c>
     </row>
-    <row r="171" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A171" s="2" t="s">
         <v>730</v>
       </c>
@@ -10221,7 +10220,7 @@
         <v>114.995</v>
       </c>
     </row>
-    <row r="172" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A172" s="2" t="s">
         <v>866</v>
       </c>
@@ -10253,7 +10252,7 @@
         <v>114.995</v>
       </c>
     </row>
-    <row r="173" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A173" s="2" t="s">
         <v>731</v>
       </c>
@@ -10285,7 +10284,7 @@
         <v>114.995</v>
       </c>
     </row>
-    <row r="174" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A174" s="2" t="s">
         <v>867</v>
       </c>
@@ -10317,7 +10316,7 @@
         <v>114.995</v>
       </c>
     </row>
-    <row r="175" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A175" s="2" t="s">
         <v>732</v>
       </c>
@@ -10349,7 +10348,7 @@
         <v>114.995</v>
       </c>
     </row>
-    <row r="176" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A176" s="2" t="s">
         <v>733</v>
       </c>
@@ -10381,7 +10380,7 @@
         <v>114.995</v>
       </c>
     </row>
-    <row r="177" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A177" s="2" t="s">
         <v>734</v>
       </c>
@@ -10413,7 +10412,7 @@
         <v>139.995</v>
       </c>
     </row>
-    <row r="178" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A178" s="2" t="s">
         <v>868</v>
       </c>
@@ -10445,7 +10444,7 @@
         <v>139.995</v>
       </c>
     </row>
-    <row r="179" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A179" s="2" t="s">
         <v>869</v>
       </c>
@@ -10477,7 +10476,7 @@
         <v>139.995</v>
       </c>
     </row>
-    <row r="180" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A180" s="2" t="s">
         <v>735</v>
       </c>
@@ -10509,7 +10508,7 @@
         <v>139.995</v>
       </c>
     </row>
-    <row r="181" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A181" s="2" t="s">
         <v>736</v>
       </c>
@@ -10541,7 +10540,7 @@
         <v>139.995</v>
       </c>
     </row>
-    <row r="182" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A182" s="2" t="s">
         <v>737</v>
       </c>
@@ -10573,7 +10572,7 @@
         <v>139.995</v>
       </c>
     </row>
-    <row r="183" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A183" s="2" t="s">
         <v>870</v>
       </c>
@@ -10605,7 +10604,7 @@
         <v>129.995</v>
       </c>
     </row>
-    <row r="184" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A184" s="2" t="s">
         <v>738</v>
       </c>
@@ -10637,7 +10636,7 @@
         <v>129.995</v>
       </c>
     </row>
-    <row r="185" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A185" s="2" t="s">
         <v>739</v>
       </c>
@@ -10669,7 +10668,7 @@
         <v>129.995</v>
       </c>
     </row>
-    <row r="186" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A186" s="2" t="s">
         <v>871</v>
       </c>
@@ -10701,7 +10700,7 @@
         <v>124.995</v>
       </c>
     </row>
-    <row r="187" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A187" s="2" t="s">
         <v>740</v>
       </c>
@@ -10733,7 +10732,7 @@
         <v>124.995</v>
       </c>
     </row>
-    <row r="188" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A188" s="2" t="s">
         <v>741</v>
       </c>
@@ -10765,7 +10764,7 @@
         <v>124.995</v>
       </c>
     </row>
-    <row r="189" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A189" s="2" t="s">
         <v>742</v>
       </c>
@@ -10797,7 +10796,7 @@
         <v>124.995</v>
       </c>
     </row>
-    <row r="190" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A190" s="2" t="s">
         <v>872</v>
       </c>
@@ -10829,7 +10828,7 @@
         <v>124.995</v>
       </c>
     </row>
-    <row r="191" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A191" s="2" t="s">
         <v>743</v>
       </c>
@@ -10861,7 +10860,7 @@
         <v>124.995</v>
       </c>
     </row>
-    <row r="192" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A192" s="2" t="s">
         <v>744</v>
       </c>
@@ -10893,7 +10892,7 @@
         <v>124.995</v>
       </c>
     </row>
-    <row r="193" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A193" s="2" t="s">
         <v>745</v>
       </c>
@@ -10925,7 +10924,7 @@
         <v>124.995</v>
       </c>
     </row>
-    <row r="194" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A194" s="2" t="s">
         <v>873</v>
       </c>
@@ -10957,7 +10956,7 @@
         <v>99.995000000000005</v>
       </c>
     </row>
-    <row r="195" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A195" s="2" t="s">
         <v>746</v>
       </c>
@@ -10989,7 +10988,7 @@
         <v>99.995000000000005</v>
       </c>
     </row>
-    <row r="196" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A196" s="2" t="s">
         <v>747</v>
       </c>
@@ -11021,7 +11020,7 @@
         <v>99.995000000000005</v>
       </c>
     </row>
-    <row r="197" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A197" s="2" t="s">
         <v>874</v>
       </c>
@@ -11053,7 +11052,7 @@
         <v>99.995000000000005</v>
       </c>
     </row>
-    <row r="198" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A198" s="2" t="s">
         <v>748</v>
       </c>
@@ -11085,7 +11084,7 @@
         <v>99.995000000000005</v>
       </c>
     </row>
-    <row r="199" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A199" s="2" t="s">
         <v>749</v>
       </c>
@@ -11117,7 +11116,7 @@
         <v>99.995000000000005</v>
       </c>
     </row>
-    <row r="200" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A200" s="2" t="s">
         <v>750</v>
       </c>
@@ -11149,7 +11148,7 @@
         <v>99.995000000000005</v>
       </c>
     </row>
-    <row r="201" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A201" s="2" t="s">
         <v>751</v>
       </c>
@@ -11181,7 +11180,7 @@
         <v>99.995000000000005</v>
       </c>
     </row>
-    <row r="202" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A202" s="2" t="s">
         <v>752</v>
       </c>
@@ -11213,7 +11212,7 @@
         <v>99.995000000000005</v>
       </c>
     </row>
-    <row r="203" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A203" s="2" t="s">
         <v>753</v>
       </c>
@@ -11245,7 +11244,7 @@
         <v>99.995000000000005</v>
       </c>
     </row>
-    <row r="204" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A204" s="2" t="s">
         <v>754</v>
       </c>
@@ -11277,7 +11276,7 @@
         <v>124.995</v>
       </c>
     </row>
-    <row r="205" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A205" s="2" t="s">
         <v>755</v>
       </c>
@@ -11309,7 +11308,7 @@
         <v>124.995</v>
       </c>
     </row>
-    <row r="206" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A206" s="2" t="s">
         <v>756</v>
       </c>
@@ -11341,7 +11340,7 @@
         <v>124.995</v>
       </c>
     </row>
-    <row r="207" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A207" s="2" t="s">
         <v>757</v>
       </c>
@@ -11373,7 +11372,7 @@
         <v>124.995</v>
       </c>
     </row>
-    <row r="208" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A208" s="2" t="s">
         <v>758</v>
       </c>
@@ -11405,7 +11404,7 @@
         <v>114.995</v>
       </c>
     </row>
-    <row r="209" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="209" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A209" s="2" t="s">
         <v>875</v>
       </c>
@@ -11437,7 +11436,7 @@
         <v>114.995</v>
       </c>
     </row>
-    <row r="210" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="210" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A210" s="2" t="s">
         <v>759</v>
       </c>
@@ -11469,7 +11468,7 @@
         <v>114.995</v>
       </c>
     </row>
-    <row r="211" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="211" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A211" s="2" t="s">
         <v>760</v>
       </c>
@@ -11501,7 +11500,7 @@
         <v>114.995</v>
       </c>
     </row>
-    <row r="212" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="212" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A212" s="2" t="s">
         <v>761</v>
       </c>
@@ -11533,7 +11532,7 @@
         <v>114.995</v>
       </c>
     </row>
-    <row r="213" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="213" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A213" s="2" t="s">
         <v>762</v>
       </c>
@@ -11565,7 +11564,7 @@
         <v>114.995</v>
       </c>
     </row>
-    <row r="214" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="214" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A214" s="2" t="s">
         <v>763</v>
       </c>
@@ -11597,7 +11596,7 @@
         <v>124.995</v>
       </c>
     </row>
-    <row r="215" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="215" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A215" s="2" t="s">
         <v>764</v>
       </c>
@@ -11629,7 +11628,7 @@
         <v>124.995</v>
       </c>
     </row>
-    <row r="216" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="216" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A216" s="2" t="s">
         <v>765</v>
       </c>
@@ -11661,7 +11660,7 @@
         <v>99.995000000000005</v>
       </c>
     </row>
-    <row r="217" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="217" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A217" s="2" t="s">
         <v>876</v>
       </c>
@@ -11693,7 +11692,7 @@
         <v>99.995000000000005</v>
       </c>
     </row>
-    <row r="218" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="218" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A218" s="2" t="s">
         <v>766</v>
       </c>
@@ -11725,7 +11724,7 @@
         <v>99.995000000000005</v>
       </c>
     </row>
-    <row r="219" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="219" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A219" s="2" t="s">
         <v>767</v>
       </c>
@@ -11757,7 +11756,7 @@
         <v>99.995000000000005</v>
       </c>
     </row>
-    <row r="220" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="220" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A220" s="2" t="s">
         <v>768</v>
       </c>
@@ -11789,7 +11788,7 @@
         <v>99.995000000000005</v>
       </c>
     </row>
-    <row r="221" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="221" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A221" s="2" t="s">
         <v>769</v>
       </c>
@@ -11821,7 +11820,7 @@
         <v>99.995000000000005</v>
       </c>
     </row>
-    <row r="222" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="222" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A222" s="2" t="s">
         <v>770</v>
       </c>
@@ -11853,7 +11852,7 @@
         <v>49.994999999999997</v>
       </c>
     </row>
-    <row r="223" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="223" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A223" s="2" t="s">
         <v>771</v>
       </c>
@@ -11885,7 +11884,7 @@
         <v>49.994999999999997</v>
       </c>
     </row>
-    <row r="224" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="224" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A224" s="2" t="s">
         <v>772</v>
       </c>
@@ -11917,7 +11916,7 @@
         <v>49.994999999999997</v>
       </c>
     </row>
-    <row r="225" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="225" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A225" s="2" t="s">
         <v>773</v>
       </c>
@@ -11949,7 +11948,7 @@
         <v>49.994999999999997</v>
       </c>
     </row>
-    <row r="226" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="226" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A226" s="2" t="s">
         <v>877</v>
       </c>
@@ -11981,7 +11980,7 @@
         <v>49.994999999999997</v>
       </c>
     </row>
-    <row r="227" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="227" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A227" s="2" t="s">
         <v>878</v>
       </c>
@@ -12013,7 +12012,7 @@
         <v>89.995000000000005</v>
       </c>
     </row>
-    <row r="228" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="228" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A228" s="2" t="s">
         <v>879</v>
       </c>
@@ -12045,7 +12044,7 @@
         <v>89.995000000000005</v>
       </c>
     </row>
-    <row r="229" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="229" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A229" s="2" t="s">
         <v>774</v>
       </c>
@@ -12077,7 +12076,7 @@
         <v>89.995000000000005</v>
       </c>
     </row>
-    <row r="230" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="230" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A230" s="2" t="s">
         <v>775</v>
       </c>
@@ -12109,7 +12108,7 @@
         <v>89.995000000000005</v>
       </c>
     </row>
-    <row r="231" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="231" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A231" s="2" t="s">
         <v>776</v>
       </c>
@@ -12141,7 +12140,7 @@
         <v>89.995000000000005</v>
       </c>
     </row>
-    <row r="232" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="232" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A232" s="2" t="s">
         <v>777</v>
       </c>
@@ -12173,7 +12172,7 @@
         <v>89.995000000000005</v>
       </c>
     </row>
-    <row r="233" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="233" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A233" s="2" t="s">
         <v>1390</v>
       </c>
@@ -12205,7 +12204,7 @@
         <v>89.995000000000005</v>
       </c>
     </row>
-    <row r="234" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="234" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A234" s="2" t="s">
         <v>1391</v>
       </c>
@@ -12237,7 +12236,7 @@
         <v>89.995000000000005</v>
       </c>
     </row>
-    <row r="235" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="235" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A235" s="2" t="s">
         <v>1392</v>
       </c>
@@ -12269,7 +12268,7 @@
         <v>89.995000000000005</v>
       </c>
     </row>
-    <row r="236" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="236" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A236" s="2" t="s">
         <v>1393</v>
       </c>
@@ -12301,7 +12300,7 @@
         <v>89.995000000000005</v>
       </c>
     </row>
-    <row r="237" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="237" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A237" s="2" t="s">
         <v>880</v>
       </c>
@@ -12333,7 +12332,7 @@
         <v>74.995000000000005</v>
       </c>
     </row>
-    <row r="238" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="238" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A238" s="2" t="s">
         <v>778</v>
       </c>
@@ -12365,7 +12364,7 @@
         <v>74.995000000000005</v>
       </c>
     </row>
-    <row r="239" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="239" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A239" s="2" t="s">
         <v>779</v>
       </c>
@@ -12397,7 +12396,7 @@
         <v>74.995000000000005</v>
       </c>
     </row>
-    <row r="240" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="240" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A240" s="2" t="s">
         <v>780</v>
       </c>
@@ -12429,7 +12428,7 @@
         <v>74.995000000000005</v>
       </c>
     </row>
-    <row r="241" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="241" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A241" s="2" t="s">
         <v>881</v>
       </c>
@@ -12461,7 +12460,7 @@
         <v>74.995000000000005</v>
       </c>
     </row>
-    <row r="242" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="242" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A242" s="2" t="s">
         <v>781</v>
       </c>
@@ -12493,7 +12492,7 @@
         <v>64.995000000000005</v>
       </c>
     </row>
-    <row r="243" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="243" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A243" s="2" t="s">
         <v>782</v>
       </c>
@@ -12525,7 +12524,7 @@
         <v>64.995000000000005</v>
       </c>
     </row>
-    <row r="244" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="244" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A244" s="2" t="s">
         <v>783</v>
       </c>
@@ -12557,7 +12556,7 @@
         <v>64.995000000000005</v>
       </c>
     </row>
-    <row r="245" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="245" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A245" s="2" t="s">
         <v>784</v>
       </c>
@@ -12589,7 +12588,7 @@
         <v>64.995000000000005</v>
       </c>
     </row>
-    <row r="246" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="246" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A246" s="2" t="s">
         <v>785</v>
       </c>
@@ -12621,7 +12620,7 @@
         <v>64.995000000000005</v>
       </c>
     </row>
-    <row r="247" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="247" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A247" s="2" t="s">
         <v>882</v>
       </c>
@@ -12653,7 +12652,7 @@
         <v>69.995000000000005</v>
       </c>
     </row>
-    <row r="248" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="248" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A248" s="2" t="s">
         <v>883</v>
       </c>
@@ -12685,7 +12684,7 @@
         <v>69.995000000000005</v>
       </c>
     </row>
-    <row r="249" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="249" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A249" s="2" t="s">
         <v>884</v>
       </c>
@@ -12717,7 +12716,7 @@
         <v>69.995000000000005</v>
       </c>
     </row>
-    <row r="250" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="250" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A250" s="2" t="s">
         <v>885</v>
       </c>
@@ -12749,7 +12748,7 @@
         <v>69.995000000000005</v>
       </c>
     </row>
-    <row r="251" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="251" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A251" s="2" t="s">
         <v>786</v>
       </c>
@@ -12781,7 +12780,7 @@
         <v>649.995</v>
       </c>
     </row>
-    <row r="252" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="252" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A252" s="2" t="s">
         <v>886</v>
       </c>
@@ -12813,7 +12812,7 @@
         <v>649.995</v>
       </c>
     </row>
-    <row r="253" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="253" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A253" s="2" t="s">
         <v>887</v>
       </c>
@@ -12845,7 +12844,7 @@
         <v>274.995</v>
       </c>
     </row>
-    <row r="254" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="254" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A254" s="2" t="s">
         <v>888</v>
       </c>
@@ -12877,7 +12876,7 @@
         <v>274.995</v>
       </c>
     </row>
-    <row r="255" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="255" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A255" s="2" t="s">
         <v>889</v>
       </c>
@@ -12909,7 +12908,7 @@
         <v>274.995</v>
       </c>
     </row>
-    <row r="256" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="256" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A256" s="2" t="s">
         <v>787</v>
       </c>
@@ -12941,7 +12940,7 @@
         <v>399.995</v>
       </c>
     </row>
-    <row r="257" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="257" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A257" s="2" t="s">
         <v>788</v>
       </c>
@@ -12973,7 +12972,7 @@
         <v>349.995</v>
       </c>
     </row>
-    <row r="258" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="258" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A258" s="2" t="s">
         <v>890</v>
       </c>
@@ -13005,7 +13004,7 @@
         <v>349.995</v>
       </c>
     </row>
-    <row r="259" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="259" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A259" s="2" t="s">
         <v>789</v>
       </c>
@@ -13037,7 +13036,7 @@
         <v>299.995</v>
       </c>
     </row>
-    <row r="260" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="260" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A260" s="2" t="s">
         <v>891</v>
       </c>
@@ -13069,7 +13068,7 @@
         <v>299.995</v>
       </c>
     </row>
-    <row r="261" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="261" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A261" s="2" t="s">
         <v>790</v>
       </c>
@@ -13101,7 +13100,7 @@
         <v>299.995</v>
       </c>
     </row>
-    <row r="262" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="262" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A262" s="2" t="s">
         <v>892</v>
       </c>
@@ -13133,7 +13132,7 @@
         <v>199.995</v>
       </c>
     </row>
-    <row r="263" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="263" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A263" s="2" t="s">
         <v>791</v>
       </c>
@@ -13165,7 +13164,7 @@
         <v>199.995</v>
       </c>
     </row>
-    <row r="264" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="264" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A264" s="2" t="s">
         <v>792</v>
       </c>
@@ -13197,7 +13196,7 @@
         <v>199.995</v>
       </c>
     </row>
-    <row r="265" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="265" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A265" s="2" t="s">
         <v>793</v>
       </c>
@@ -13229,7 +13228,7 @@
         <v>199.995</v>
       </c>
     </row>
-    <row r="266" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="266" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A266" s="2" t="s">
         <v>794</v>
       </c>
@@ -13261,7 +13260,7 @@
         <v>199.995</v>
       </c>
     </row>
-    <row r="267" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="267" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A267" s="2" t="s">
         <v>795</v>
       </c>
@@ -13293,7 +13292,7 @@
         <v>199.995</v>
       </c>
     </row>
-    <row r="268" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="268" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A268" s="2" t="s">
         <v>796</v>
       </c>
@@ -13325,7 +13324,7 @@
         <v>199.995</v>
       </c>
     </row>
-    <row r="269" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="269" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A269" s="2" t="s">
         <v>797</v>
       </c>
@@ -13357,7 +13356,7 @@
         <v>164.995</v>
       </c>
     </row>
-    <row r="270" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="270" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A270" s="2" t="s">
         <v>798</v>
       </c>
@@ -13389,7 +13388,7 @@
         <v>164.995</v>
       </c>
     </row>
-    <row r="271" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="271" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A271" s="2" t="s">
         <v>799</v>
       </c>
@@ -13421,7 +13420,7 @@
         <v>164.995</v>
       </c>
     </row>
-    <row r="272" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="272" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A272" s="2" t="s">
         <v>893</v>
       </c>
@@ -13453,7 +13452,7 @@
         <v>164.995</v>
       </c>
     </row>
-    <row r="273" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="273" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A273" s="2" t="s">
         <v>800</v>
       </c>
@@ -13741,7 +13740,7 @@
         <v>189.995</v>
       </c>
     </row>
-    <row r="282" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="282" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A282" s="2" t="s">
         <v>897</v>
       </c>
@@ -13773,7 +13772,7 @@
         <v>174.995</v>
       </c>
     </row>
-    <row r="283" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="283" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A283" s="2" t="s">
         <v>805</v>
       </c>
@@ -13805,7 +13804,7 @@
         <v>174.995</v>
       </c>
     </row>
-    <row r="284" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="284" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A284" s="2" t="s">
         <v>898</v>
       </c>
@@ -13837,7 +13836,7 @@
         <v>174.995</v>
       </c>
     </row>
-    <row r="285" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="285" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A285" s="2" t="s">
         <v>806</v>
       </c>
@@ -13869,7 +13868,7 @@
         <v>174.995</v>
       </c>
     </row>
-    <row r="286" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="286" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A286" s="2" t="s">
         <v>807</v>
       </c>
@@ -13901,7 +13900,7 @@
         <v>164.995</v>
       </c>
     </row>
-    <row r="287" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="287" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A287" s="2" t="s">
         <v>808</v>
       </c>
@@ -13933,7 +13932,7 @@
         <v>164.995</v>
       </c>
     </row>
-    <row r="288" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="288" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A288" s="2" t="s">
         <v>809</v>
       </c>
@@ -13965,7 +13964,7 @@
         <v>164.995</v>
       </c>
     </row>
-    <row r="289" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="289" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A289" s="2" t="s">
         <v>810</v>
       </c>
@@ -13997,7 +13996,7 @@
         <v>164.995</v>
       </c>
     </row>
-    <row r="290" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="290" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A290" s="2" t="s">
         <v>811</v>
       </c>
@@ -14029,7 +14028,7 @@
         <v>164.995</v>
       </c>
     </row>
-    <row r="291" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="291" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A291" s="2" t="s">
         <v>812</v>
       </c>
@@ -14061,7 +14060,7 @@
         <v>149.995</v>
       </c>
     </row>
-    <row r="292" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="292" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A292" s="2" t="s">
         <v>813</v>
       </c>
@@ -14093,7 +14092,7 @@
         <v>149.995</v>
       </c>
     </row>
-    <row r="293" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="293" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A293" s="2" t="s">
         <v>814</v>
       </c>
@@ -14125,7 +14124,7 @@
         <v>149.995</v>
       </c>
     </row>
-    <row r="294" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="294" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A294" s="2" t="s">
         <v>815</v>
       </c>
@@ -14157,7 +14156,7 @@
         <v>149.995</v>
       </c>
     </row>
-    <row r="295" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="295" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A295" s="2" t="s">
         <v>899</v>
       </c>
@@ -14189,7 +14188,7 @@
         <v>164.995</v>
       </c>
     </row>
-    <row r="296" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="296" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A296" s="2" t="s">
         <v>816</v>
       </c>
@@ -14221,7 +14220,7 @@
         <v>164.995</v>
       </c>
     </row>
-    <row r="297" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="297" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A297" s="2" t="s">
         <v>817</v>
       </c>
@@ -14253,7 +14252,7 @@
         <v>164.995</v>
       </c>
     </row>
-    <row r="298" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="298" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A298" s="2" t="s">
         <v>818</v>
       </c>
@@ -14285,7 +14284,7 @@
         <v>164.995</v>
       </c>
     </row>
-    <row r="299" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="299" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A299" s="2" t="s">
         <v>819</v>
       </c>
@@ -14317,7 +14316,7 @@
         <v>164.995</v>
       </c>
     </row>
-    <row r="300" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="300" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A300" s="2" t="s">
         <v>900</v>
       </c>
@@ -14349,7 +14348,7 @@
         <v>164.995</v>
       </c>
     </row>
-    <row r="301" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="301" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A301" s="2" t="s">
         <v>820</v>
       </c>
@@ -14381,7 +14380,7 @@
         <v>149.995</v>
       </c>
     </row>
-    <row r="302" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="302" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A302" s="2" t="s">
         <v>821</v>
       </c>
@@ -14413,7 +14412,7 @@
         <v>149.995</v>
       </c>
     </row>
-    <row r="303" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="303" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A303" s="2" t="s">
         <v>822</v>
       </c>
@@ -14445,7 +14444,7 @@
         <v>149.995</v>
       </c>
     </row>
-    <row r="304" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="304" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A304" s="2" t="s">
         <v>823</v>
       </c>
@@ -14477,7 +14476,7 @@
         <v>149.995</v>
       </c>
     </row>
-    <row r="305" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="305" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A305" s="2" t="s">
         <v>824</v>
       </c>
@@ -14509,7 +14508,7 @@
         <v>149.995</v>
       </c>
     </row>
-    <row r="306" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="306" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A306" s="2" t="s">
         <v>901</v>
       </c>
@@ -14541,7 +14540,7 @@
         <v>199.995</v>
       </c>
     </row>
-    <row r="307" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="307" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A307" s="2" t="s">
         <v>825</v>
       </c>
@@ -14573,7 +14572,7 @@
         <v>199.995</v>
       </c>
     </row>
-    <row r="308" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="308" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A308" s="2" t="s">
         <v>826</v>
       </c>
@@ -14605,7 +14604,7 @@
         <v>199.995</v>
       </c>
     </row>
-    <row r="309" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="309" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A309" s="2" t="s">
         <v>902</v>
       </c>
@@ -14637,7 +14636,7 @@
         <v>249.995</v>
       </c>
     </row>
-    <row r="310" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="310" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A310" s="2" t="s">
         <v>903</v>
       </c>
@@ -14669,7 +14668,7 @@
         <v>249.995</v>
       </c>
     </row>
-    <row r="311" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="311" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A311" s="2" t="s">
         <v>904</v>
       </c>
@@ -14701,7 +14700,7 @@
         <v>59.994999999999997</v>
       </c>
     </row>
-    <row r="312" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="312" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A312" s="2" t="s">
         <v>905</v>
       </c>
@@ -14733,7 +14732,7 @@
         <v>59.994999999999997</v>
       </c>
     </row>
-    <row r="313" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="313" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A313" s="2" t="s">
         <v>906</v>
       </c>
@@ -14765,7 +14764,7 @@
         <v>59.994999999999997</v>
       </c>
     </row>
-    <row r="314" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="314" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A314" s="2" t="s">
         <v>907</v>
       </c>
@@ -14797,7 +14796,7 @@
         <v>54.994999999999997</v>
       </c>
     </row>
-    <row r="315" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="315" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A315" s="2" t="s">
         <v>908</v>
       </c>
@@ -14829,7 +14828,7 @@
         <v>54.994999999999997</v>
       </c>
     </row>
-    <row r="316" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="316" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A316" s="2" t="s">
         <v>909</v>
       </c>
@@ -14861,7 +14860,7 @@
         <v>54.994999999999997</v>
       </c>
     </row>
-    <row r="317" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="317" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A317" s="2" t="s">
         <v>910</v>
       </c>
@@ -14893,7 +14892,7 @@
         <v>59.994999999999997</v>
       </c>
     </row>
-    <row r="318" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="318" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A318" s="2" t="s">
         <v>911</v>
       </c>
@@ -14925,7 +14924,7 @@
         <v>64.995000000000005</v>
       </c>
     </row>
-    <row r="319" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="319" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A319" s="2" t="s">
         <v>912</v>
       </c>
@@ -14957,7 +14956,7 @@
         <v>84.995000000000005</v>
       </c>
     </row>
-    <row r="320" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="320" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A320" s="2" t="s">
         <v>913</v>
       </c>
@@ -14989,7 +14988,7 @@
         <v>84.995000000000005</v>
       </c>
     </row>
-    <row r="321" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="321" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A321" s="2" t="s">
         <v>914</v>
       </c>
@@ -15021,7 +15020,7 @@
         <v>84.995000000000005</v>
       </c>
     </row>
-    <row r="322" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="322" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A322" s="2" t="s">
         <v>915</v>
       </c>
@@ -15053,7 +15052,7 @@
         <v>74.995000000000005</v>
       </c>
     </row>
-    <row r="323" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="323" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A323" s="2" t="s">
         <v>916</v>
       </c>
@@ -15085,7 +15084,7 @@
         <v>74.995000000000005</v>
       </c>
     </row>
-    <row r="324" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="324" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A324" s="2" t="s">
         <v>917</v>
       </c>
@@ -15117,7 +15116,7 @@
         <v>74.995000000000005</v>
       </c>
     </row>
-    <row r="325" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="325" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A325" s="2" t="s">
         <v>918</v>
       </c>
@@ -15149,7 +15148,7 @@
         <v>69.995000000000005</v>
       </c>
     </row>
-    <row r="326" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="326" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A326" s="2" t="s">
         <v>919</v>
       </c>
@@ -15181,7 +15180,7 @@
         <v>69.995000000000005</v>
       </c>
     </row>
-    <row r="327" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="327" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A327" s="2" t="s">
         <v>920</v>
       </c>
@@ -15213,7 +15212,7 @@
         <v>59.994999999999997</v>
       </c>
     </row>
-    <row r="328" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="328" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A328" s="2" t="s">
         <v>921</v>
       </c>
@@ -15245,7 +15244,7 @@
         <v>59.994999999999997</v>
       </c>
     </row>
-    <row r="329" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="329" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A329" s="2" t="s">
         <v>922</v>
       </c>
@@ -15277,7 +15276,7 @@
         <v>89.995000000000005</v>
       </c>
     </row>
-    <row r="330" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="330" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A330" s="2" t="s">
         <v>923</v>
       </c>
@@ -15309,7 +15308,7 @@
         <v>89.995000000000005</v>
       </c>
     </row>
-    <row r="331" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="331" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A331" s="2" t="s">
         <v>924</v>
       </c>
@@ -15341,7 +15340,7 @@
         <v>114.995</v>
       </c>
     </row>
-    <row r="332" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="332" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A332" s="2" t="s">
         <v>925</v>
       </c>
@@ -15373,7 +15372,7 @@
         <v>114.995</v>
       </c>
     </row>
-    <row r="333" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="333" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A333" s="2" t="s">
         <v>926</v>
       </c>
@@ -15405,7 +15404,7 @@
         <v>114.995</v>
       </c>
     </row>
-    <row r="334" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="334" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A334" s="2" t="s">
         <v>927</v>
       </c>
@@ -15437,7 +15436,7 @@
         <v>114.995</v>
       </c>
     </row>
-    <row r="335" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="335" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A335" s="2" t="s">
         <v>928</v>
       </c>
@@ -15469,7 +15468,7 @@
         <v>114.995</v>
       </c>
     </row>
-    <row r="336" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="336" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A336" s="2" t="s">
         <v>929</v>
       </c>
@@ -15501,7 +15500,7 @@
         <v>74.995000000000005</v>
       </c>
     </row>
-    <row r="337" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="337" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A337" s="2" t="s">
         <v>930</v>
       </c>
@@ -15533,7 +15532,7 @@
         <v>199.995</v>
       </c>
     </row>
-    <row r="338" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="338" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A338" s="2" t="s">
         <v>931</v>
       </c>
@@ -15565,7 +15564,7 @@
         <v>199.995</v>
       </c>
     </row>
-    <row r="339" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="339" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A339" s="2" t="s">
         <v>932</v>
       </c>
@@ -15597,7 +15596,7 @@
         <v>59.994999999999997</v>
       </c>
     </row>
-    <row r="340" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="340" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A340" s="2" t="s">
         <v>933</v>
       </c>
@@ -15629,7 +15628,7 @@
         <v>59.994999999999997</v>
       </c>
     </row>
-    <row r="341" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="341" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A341" s="2" t="s">
         <v>934</v>
       </c>
@@ -15661,7 +15660,7 @@
         <v>64.995000000000005</v>
       </c>
     </row>
-    <row r="342" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="342" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A342" s="2" t="s">
         <v>935</v>
       </c>
@@ -15693,7 +15692,7 @@
         <v>64.995000000000005</v>
       </c>
     </row>
-    <row r="343" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="343" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A343" s="2" t="s">
         <v>936</v>
       </c>
@@ -15725,7 +15724,7 @@
         <v>64.995000000000005</v>
       </c>
     </row>
-    <row r="344" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="344" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A344" s="2" t="s">
         <v>937</v>
       </c>
@@ -15757,7 +15756,7 @@
         <v>64.995000000000005</v>
       </c>
     </row>
-    <row r="345" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="345" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A345" s="2" t="s">
         <v>938</v>
       </c>
@@ -15789,7 +15788,7 @@
         <v>64.995000000000005</v>
       </c>
     </row>
-    <row r="346" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="346" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A346" s="2" t="s">
         <v>939</v>
       </c>
@@ -15821,7 +15820,7 @@
         <v>114.995</v>
       </c>
     </row>
-    <row r="347" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="347" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A347" s="2" t="s">
         <v>940</v>
       </c>
@@ -15853,7 +15852,7 @@
         <v>114.995</v>
       </c>
     </row>
-    <row r="348" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="348" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A348" s="2" t="s">
         <v>941</v>
       </c>
@@ -15885,7 +15884,7 @@
         <v>114.995</v>
       </c>
     </row>
-    <row r="349" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="349" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A349" s="2" t="s">
         <v>942</v>
       </c>
@@ -15917,7 +15916,7 @@
         <v>89.995000000000005</v>
       </c>
     </row>
-    <row r="350" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="350" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A350" s="2" t="s">
         <v>943</v>
       </c>
@@ -15949,7 +15948,7 @@
         <v>89.995000000000005</v>
       </c>
     </row>
-    <row r="351" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="351" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A351" s="2" t="s">
         <v>944</v>
       </c>
@@ -15981,7 +15980,7 @@
         <v>99.995000000000005</v>
       </c>
     </row>
-    <row r="352" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="352" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A352" s="2" t="s">
         <v>945</v>
       </c>
@@ -16013,7 +16012,7 @@
         <v>99.995000000000005</v>
       </c>
     </row>
-    <row r="353" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="353" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A353" s="2" t="s">
         <v>946</v>
       </c>
@@ -16045,7 +16044,7 @@
         <v>199.995</v>
       </c>
     </row>
-    <row r="354" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="354" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A354" s="2" t="s">
         <v>947</v>
       </c>
@@ -16077,7 +16076,7 @@
         <v>199.995</v>
       </c>
     </row>
-    <row r="355" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="355" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A355" s="2" t="s">
         <v>948</v>
       </c>
@@ -16109,7 +16108,7 @@
         <v>124.995</v>
       </c>
     </row>
-    <row r="356" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="356" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A356" s="2" t="s">
         <v>949</v>
       </c>
@@ -16141,7 +16140,7 @@
         <v>124.995</v>
       </c>
     </row>
-    <row r="357" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="357" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A357" s="2" t="s">
         <v>950</v>
       </c>
@@ -16173,7 +16172,7 @@
         <v>124.995</v>
       </c>
     </row>
-    <row r="358" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="358" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A358" s="2" t="s">
         <v>951</v>
       </c>
@@ -16205,7 +16204,7 @@
         <v>124.995</v>
       </c>
     </row>
-    <row r="359" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="359" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A359" s="2" t="s">
         <v>952</v>
       </c>
@@ -16237,7 +16236,7 @@
         <v>74.995000000000005</v>
       </c>
     </row>
-    <row r="360" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="360" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A360" s="2" t="s">
         <v>953</v>
       </c>
@@ -16269,7 +16268,7 @@
         <v>69.995000000000005</v>
       </c>
     </row>
-    <row r="361" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="361" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A361" s="2" t="s">
         <v>954</v>
       </c>
@@ -16301,7 +16300,7 @@
         <v>69.995000000000005</v>
       </c>
     </row>
-    <row r="362" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="362" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A362" s="2" t="s">
         <v>955</v>
       </c>
@@ -16333,7 +16332,7 @@
         <v>69.995000000000005</v>
       </c>
     </row>
-    <row r="363" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="363" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A363" s="2" t="s">
         <v>956</v>
       </c>
@@ -16365,7 +16364,7 @@
         <v>69.995000000000005</v>
       </c>
     </row>
-    <row r="364" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="364" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A364" s="2" t="s">
         <v>957</v>
       </c>
@@ -16397,7 +16396,7 @@
         <v>69.995000000000005</v>
       </c>
     </row>
-    <row r="365" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="365" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A365" s="2" t="s">
         <v>958</v>
       </c>
@@ -16429,7 +16428,7 @@
         <v>69.995000000000005</v>
       </c>
     </row>
-    <row r="366" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="366" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A366" s="2" t="s">
         <v>959</v>
       </c>
@@ -16461,7 +16460,7 @@
         <v>84.995000000000005</v>
       </c>
     </row>
-    <row r="367" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="367" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A367" s="2" t="s">
         <v>960</v>
       </c>
@@ -16493,7 +16492,7 @@
         <v>84.995000000000005</v>
       </c>
     </row>
-    <row r="368" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="368" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A368" s="2" t="s">
         <v>961</v>
       </c>
@@ -16525,7 +16524,7 @@
         <v>84.995000000000005</v>
       </c>
     </row>
-    <row r="369" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="369" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A369" s="2" t="s">
         <v>962</v>
       </c>
@@ -16557,7 +16556,7 @@
         <v>84.995000000000005</v>
       </c>
     </row>
-    <row r="370" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="370" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A370" s="2" t="s">
         <v>963</v>
       </c>
@@ -16589,7 +16588,7 @@
         <v>84.995000000000005</v>
       </c>
     </row>
-    <row r="371" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="371" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A371" s="2" t="s">
         <v>964</v>
       </c>
@@ -16621,7 +16620,7 @@
         <v>84.995000000000005</v>
       </c>
     </row>
-    <row r="372" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="372" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A372" s="2" t="s">
         <v>965</v>
       </c>
@@ -16653,7 +16652,7 @@
         <v>84.995000000000005</v>
       </c>
     </row>
-    <row r="373" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="373" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A373" s="2" t="s">
         <v>966</v>
       </c>
@@ -16685,7 +16684,7 @@
         <v>59.994999999999997</v>
       </c>
     </row>
-    <row r="374" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="374" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A374" s="2" t="s">
         <v>967</v>
       </c>
@@ -16717,7 +16716,7 @@
         <v>59.994999999999997</v>
       </c>
     </row>
-    <row r="375" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="375" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A375" s="2" t="s">
         <v>968</v>
       </c>
@@ -16749,7 +16748,7 @@
         <v>59.994999999999997</v>
       </c>
     </row>
-    <row r="376" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="376" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A376" s="2" t="s">
         <v>969</v>
       </c>
@@ -16781,7 +16780,7 @@
         <v>59.994999999999997</v>
       </c>
     </row>
-    <row r="377" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="377" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A377" s="2" t="s">
         <v>970</v>
       </c>
@@ -16813,7 +16812,7 @@
         <v>59.994999999999997</v>
       </c>
     </row>
-    <row r="378" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="378" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A378" s="2" t="s">
         <v>971</v>
       </c>
@@ -16845,7 +16844,7 @@
         <v>59.994999999999997</v>
       </c>
     </row>
-    <row r="379" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="379" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A379" s="2" t="s">
         <v>972</v>
       </c>
@@ -16877,7 +16876,7 @@
         <v>59.994999999999997</v>
       </c>
     </row>
-    <row r="380" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="380" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A380" s="2" t="s">
         <v>973</v>
       </c>
@@ -16909,7 +16908,7 @@
         <v>49.994999999999997</v>
       </c>
     </row>
-    <row r="381" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="381" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A381" s="2" t="s">
         <v>974</v>
       </c>
@@ -16941,7 +16940,7 @@
         <v>49.994999999999997</v>
       </c>
     </row>
-    <row r="382" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="382" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A382" s="2" t="s">
         <v>975</v>
       </c>
@@ -16973,7 +16972,7 @@
         <v>49.994999999999997</v>
       </c>
     </row>
-    <row r="383" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="383" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A383" s="2" t="s">
         <v>976</v>
       </c>
@@ -17005,7 +17004,7 @@
         <v>49.994999999999997</v>
       </c>
     </row>
-    <row r="384" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="384" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A384" s="2" t="s">
         <v>977</v>
       </c>
@@ -17037,7 +17036,7 @@
         <v>49.994999999999997</v>
       </c>
     </row>
-    <row r="385" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="385" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A385" s="2" t="s">
         <v>978</v>
       </c>
@@ -17069,7 +17068,7 @@
         <v>44.994999999999997</v>
       </c>
     </row>
-    <row r="386" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="386" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A386" s="2" t="s">
         <v>979</v>
       </c>
@@ -17101,7 +17100,7 @@
         <v>44.994999999999997</v>
       </c>
     </row>
-    <row r="387" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="387" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A387" s="2" t="s">
         <v>980</v>
       </c>
@@ -17133,7 +17132,7 @@
         <v>44.994999999999997</v>
       </c>
     </row>
-    <row r="388" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="388" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A388" s="2" t="s">
         <v>981</v>
       </c>
@@ -17165,7 +17164,7 @@
         <v>44.994999999999997</v>
       </c>
     </row>
-    <row r="389" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="389" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A389" s="2" t="s">
         <v>982</v>
       </c>
@@ -17197,7 +17196,7 @@
         <v>44.994999999999997</v>
       </c>
     </row>
-    <row r="390" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="390" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A390" s="2" t="s">
         <v>983</v>
       </c>
@@ -17229,7 +17228,7 @@
         <v>44.994999999999997</v>
       </c>
     </row>
-    <row r="391" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="391" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A391" s="2" t="s">
         <v>984</v>
       </c>
@@ -17261,7 +17260,7 @@
         <v>39.994999999999997</v>
       </c>
     </row>
-    <row r="392" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="392" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A392" s="2" t="s">
         <v>985</v>
       </c>
@@ -17293,7 +17292,7 @@
         <v>39.994999999999997</v>
       </c>
     </row>
-    <row r="393" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="393" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A393" s="2" t="s">
         <v>986</v>
       </c>
@@ -17325,7 +17324,7 @@
         <v>12.494999999999999</v>
       </c>
     </row>
-    <row r="394" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="394" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A394" s="2" t="s">
         <v>987</v>
       </c>
@@ -17357,7 +17356,7 @@
         <v>12.494999999999999</v>
       </c>
     </row>
-    <row r="395" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="395" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A395" s="2" t="s">
         <v>988</v>
       </c>
@@ -17389,7 +17388,7 @@
         <v>12.494999999999999</v>
       </c>
     </row>
-    <row r="396" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="396" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A396" s="2" t="s">
         <v>989</v>
       </c>
@@ -17421,7 +17420,7 @@
         <v>12.494999999999999</v>
       </c>
     </row>
-    <row r="397" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="397" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A397" s="2" t="s">
         <v>990</v>
       </c>
@@ -17453,7 +17452,7 @@
         <v>12.494999999999999</v>
       </c>
     </row>
-    <row r="398" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="398" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A398" s="2" t="s">
         <v>991</v>
       </c>
@@ -17485,7 +17484,7 @@
         <v>10.994999999999999</v>
       </c>
     </row>
-    <row r="399" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="399" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A399" s="2" t="s">
         <v>992</v>
       </c>
@@ -17517,7 +17516,7 @@
         <v>10.994999999999999</v>
       </c>
     </row>
-    <row r="400" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="400" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A400" s="2" t="s">
         <v>993</v>
       </c>
@@ -17549,7 +17548,7 @@
         <v>10.994999999999999</v>
       </c>
     </row>
-    <row r="401" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="401" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A401" s="2" t="s">
         <v>994</v>
       </c>
@@ -17581,7 +17580,7 @@
         <v>10.994999999999999</v>
       </c>
     </row>
-    <row r="402" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="402" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A402" s="2" t="s">
         <v>995</v>
       </c>
@@ -17613,7 +17612,7 @@
         <v>10.994999999999999</v>
       </c>
     </row>
-    <row r="403" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="403" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A403" s="2" t="s">
         <v>996</v>
       </c>
@@ -17645,7 +17644,7 @@
         <v>10.994999999999999</v>
       </c>
     </row>
-    <row r="404" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="404" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A404" s="2" t="s">
         <v>997</v>
       </c>
@@ -17677,7 +17676,7 @@
         <v>9.9949999999999992</v>
       </c>
     </row>
-    <row r="405" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="405" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A405" s="2" t="s">
         <v>998</v>
       </c>
@@ -17709,7 +17708,7 @@
         <v>9.9949999999999992</v>
       </c>
     </row>
-    <row r="406" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="406" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A406" s="2" t="s">
         <v>999</v>
       </c>
@@ -17741,7 +17740,7 @@
         <v>9.9949999999999992</v>
       </c>
     </row>
-    <row r="407" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="407" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A407" s="2" t="s">
         <v>1000</v>
       </c>
@@ -17773,7 +17772,7 @@
         <v>9.9949999999999992</v>
       </c>
     </row>
-    <row r="408" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="408" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A408" s="2" t="s">
         <v>1001</v>
       </c>
@@ -17805,7 +17804,7 @@
         <v>9.9949999999999992</v>
       </c>
     </row>
-    <row r="409" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="409" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A409" s="2" t="s">
         <v>1002</v>
       </c>
@@ -17837,7 +17836,7 @@
         <v>9.9949999999999992</v>
       </c>
     </row>
-    <row r="410" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="410" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A410" s="2" t="s">
         <v>1003</v>
       </c>
@@ -17869,7 +17868,7 @@
         <v>23.995000000000001</v>
       </c>
     </row>
-    <row r="411" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="411" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A411" s="2" t="s">
         <v>1004</v>
       </c>
@@ -17901,7 +17900,7 @@
         <v>23.995000000000001</v>
       </c>
     </row>
-    <row r="412" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="412" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A412" s="2" t="s">
         <v>1005</v>
       </c>
@@ -17933,7 +17932,7 @@
         <v>23.995000000000001</v>
       </c>
     </row>
-    <row r="413" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="413" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A413" s="2" t="s">
         <v>1006</v>
       </c>
@@ -17965,7 +17964,7 @@
         <v>21.495000000000001</v>
       </c>
     </row>
-    <row r="414" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="414" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A414" s="2" t="s">
         <v>1007</v>
       </c>
@@ -17997,7 +17996,7 @@
         <v>21.495000000000001</v>
       </c>
     </row>
-    <row r="415" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="415" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A415" s="2" t="s">
         <v>1008</v>
       </c>
@@ -18029,7 +18028,7 @@
         <v>21.495000000000001</v>
       </c>
     </row>
-    <row r="416" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="416" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A416" s="2" t="s">
         <v>1009</v>
       </c>
@@ -18061,7 +18060,7 @@
         <v>19.995000000000001</v>
       </c>
     </row>
-    <row r="417" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="417" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A417" s="2" t="s">
         <v>1010</v>
       </c>
@@ -18093,7 +18092,7 @@
         <v>19.995000000000001</v>
       </c>
     </row>
-    <row r="418" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="418" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A418" s="2" t="s">
         <v>1011</v>
       </c>
@@ -18125,7 +18124,7 @@
         <v>19.995000000000001</v>
       </c>
     </row>
-    <row r="419" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="419" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A419" s="2" t="s">
         <v>1012</v>
       </c>
@@ -18157,7 +18156,7 @@
         <v>19.995000000000001</v>
       </c>
     </row>
-    <row r="420" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="420" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A420" s="2" t="s">
         <v>1013</v>
       </c>
@@ -18189,7 +18188,7 @@
         <v>19.995000000000001</v>
       </c>
     </row>
-    <row r="421" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="421" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A421" s="2" t="s">
         <v>1014</v>
       </c>
@@ -18221,7 +18220,7 @@
         <v>19.995000000000001</v>
       </c>
     </row>
-    <row r="422" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="422" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A422" s="2" t="s">
         <v>1015</v>
       </c>
@@ -18253,7 +18252,7 @@
         <v>19.995000000000001</v>
       </c>
     </row>
-    <row r="423" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="423" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A423" s="2" t="s">
         <v>1016</v>
       </c>
@@ -18285,7 +18284,7 @@
         <v>19.995000000000001</v>
       </c>
     </row>
-    <row r="424" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="424" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A424" s="2" t="s">
         <v>1017</v>
       </c>
@@ -18317,7 +18316,7 @@
         <v>19.995000000000001</v>
       </c>
     </row>
-    <row r="425" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="425" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A425" s="2" t="s">
         <v>1018</v>
       </c>
@@ -18349,7 +18348,7 @@
         <v>19.995000000000001</v>
       </c>
     </row>
-    <row r="426" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="426" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A426" s="2" t="s">
         <v>1019</v>
       </c>
@@ -18381,7 +18380,7 @@
         <v>12.494999999999999</v>
       </c>
     </row>
-    <row r="427" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="427" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A427" s="2" t="s">
         <v>1020</v>
       </c>
@@ -18413,7 +18412,7 @@
         <v>12.494999999999999</v>
       </c>
     </row>
-    <row r="428" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="428" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A428" s="2" t="s">
         <v>1021</v>
       </c>
@@ -18445,7 +18444,7 @@
         <v>12.494999999999999</v>
       </c>
     </row>
-    <row r="429" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="429" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A429" s="2" t="s">
         <v>1022</v>
       </c>
@@ -18477,7 +18476,7 @@
         <v>12.494999999999999</v>
       </c>
     </row>
-    <row r="430" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="430" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A430" s="2" t="s">
         <v>1023</v>
       </c>
@@ -18509,7 +18508,7 @@
         <v>12.494999999999999</v>
       </c>
     </row>
-    <row r="431" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="431" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A431" s="2" t="s">
         <v>1024</v>
       </c>
@@ -18541,7 +18540,7 @@
         <v>10.994999999999999</v>
       </c>
     </row>
-    <row r="432" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="432" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A432" s="2" t="s">
         <v>1025</v>
       </c>
@@ -18573,7 +18572,7 @@
         <v>10.994999999999999</v>
       </c>
     </row>
-    <row r="433" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="433" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A433" s="2" t="s">
         <v>1026</v>
       </c>
@@ -18605,7 +18604,7 @@
         <v>10.994999999999999</v>
       </c>
     </row>
-    <row r="434" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="434" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A434" s="2" t="s">
         <v>1027</v>
       </c>
@@ -18637,7 +18636,7 @@
         <v>10.994999999999999</v>
       </c>
     </row>
-    <row r="435" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="435" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A435" s="2" t="s">
         <v>1028</v>
       </c>
@@ -18669,7 +18668,7 @@
         <v>10.994999999999999</v>
       </c>
     </row>
-    <row r="436" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="436" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A436" s="2" t="s">
         <v>1029</v>
       </c>
@@ -18701,7 +18700,7 @@
         <v>10.994999999999999</v>
       </c>
     </row>
-    <row r="437" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="437" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A437" s="2" t="s">
         <v>1030</v>
       </c>
@@ -18733,7 +18732,7 @@
         <v>9.9949999999999992</v>
       </c>
     </row>
-    <row r="438" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="438" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A438" s="2" t="s">
         <v>1031</v>
       </c>
@@ -18765,7 +18764,7 @@
         <v>9.9949999999999992</v>
       </c>
     </row>
-    <row r="439" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="439" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A439" s="2" t="s">
         <v>1032</v>
       </c>
@@ -18797,7 +18796,7 @@
         <v>9.9949999999999992</v>
       </c>
     </row>
-    <row r="440" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="440" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A440" s="2" t="s">
         <v>1033</v>
       </c>
@@ -18829,7 +18828,7 @@
         <v>9.9949999999999992</v>
       </c>
     </row>
-    <row r="441" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="441" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A441" s="2" t="s">
         <v>1034</v>
       </c>
@@ -18861,7 +18860,7 @@
         <v>9.9949999999999992</v>
       </c>
     </row>
-    <row r="442" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="442" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A442" s="2" t="s">
         <v>1035</v>
       </c>
@@ -18893,7 +18892,7 @@
         <v>9.9949999999999992</v>
       </c>
     </row>
-    <row r="443" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="443" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A443" s="2" t="s">
         <v>1036</v>
       </c>
@@ -18925,7 +18924,7 @@
         <v>9.9949999999999992</v>
       </c>
     </row>
-    <row r="444" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="444" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A444" s="2" t="s">
         <v>1037</v>
       </c>
@@ -18957,7 +18956,7 @@
         <v>9.9949999999999992</v>
       </c>
     </row>
-    <row r="445" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="445" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A445" s="2" t="s">
         <v>1038</v>
       </c>
@@ -18989,7 +18988,7 @@
         <v>9.9949999999999992</v>
       </c>
     </row>
-    <row r="446" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="446" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A446" s="2" t="s">
         <v>1039</v>
       </c>
@@ -19021,7 +19020,7 @@
         <v>23.995000000000001</v>
       </c>
     </row>
-    <row r="447" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="447" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A447" s="2" t="s">
         <v>1040</v>
       </c>
@@ -19053,7 +19052,7 @@
         <v>23.995000000000001</v>
       </c>
     </row>
-    <row r="448" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="448" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A448" s="2" t="s">
         <v>1041</v>
       </c>
@@ -19085,7 +19084,7 @@
         <v>23.995000000000001</v>
       </c>
     </row>
-    <row r="449" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="449" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A449" s="2" t="s">
         <v>1042</v>
       </c>
@@ -19117,7 +19116,7 @@
         <v>21.495000000000001</v>
       </c>
     </row>
-    <row r="450" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="450" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A450" s="2" t="s">
         <v>1043</v>
       </c>
@@ -19149,7 +19148,7 @@
         <v>21.495000000000001</v>
       </c>
     </row>
-    <row r="451" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="451" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A451" s="2" t="s">
         <v>1044</v>
       </c>
@@ -19181,7 +19180,7 @@
         <v>21.495000000000001</v>
       </c>
     </row>
-    <row r="452" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="452" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A452" s="2" t="s">
         <v>1045</v>
       </c>
@@ -19213,7 +19212,7 @@
         <v>19.995000000000001</v>
       </c>
     </row>
-    <row r="453" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="453" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A453" s="2" t="s">
         <v>1046</v>
       </c>
@@ -19245,7 +19244,7 @@
         <v>19.995000000000001</v>
       </c>
     </row>
-    <row r="454" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="454" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A454" s="2" t="s">
         <v>1047</v>
       </c>
@@ -19277,7 +19276,7 @@
         <v>19.995000000000001</v>
       </c>
     </row>
-    <row r="455" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="455" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A455" s="2" t="s">
         <v>1048</v>
       </c>
@@ -19309,7 +19308,7 @@
         <v>19.995000000000001</v>
       </c>
     </row>
-    <row r="456" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="456" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A456" s="2" t="s">
         <v>1049</v>
       </c>
@@ -19341,7 +19340,7 @@
         <v>19.995000000000001</v>
       </c>
     </row>
-    <row r="457" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="457" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A457" s="2" t="s">
         <v>1050</v>
       </c>
@@ -19373,7 +19372,7 @@
         <v>19.995000000000001</v>
       </c>
     </row>
-    <row r="458" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="458" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A458" s="2" t="s">
         <v>1051</v>
       </c>
@@ -19405,7 +19404,7 @@
         <v>19.995000000000001</v>
       </c>
     </row>
-    <row r="459" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="459" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A459" s="2" t="s">
         <v>1052</v>
       </c>
@@ -19437,7 +19436,7 @@
         <v>19.995000000000001</v>
       </c>
     </row>
-    <row r="460" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="460" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A460" s="2" t="s">
         <v>1053</v>
       </c>
@@ -19469,7 +19468,7 @@
         <v>19.995000000000001</v>
       </c>
     </row>
-    <row r="461" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="461" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A461" s="2" t="s">
         <v>1054</v>
       </c>
@@ -19501,7 +19500,7 @@
         <v>19.995000000000001</v>
       </c>
     </row>
-    <row r="462" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="462" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A462" s="2" t="s">
         <v>1055</v>
       </c>
@@ -19533,7 +19532,7 @@
         <v>99.995000000000005</v>
       </c>
     </row>
-    <row r="463" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="463" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A463" s="2" t="s">
         <v>1056</v>
       </c>
@@ -19565,7 +19564,7 @@
         <v>99.995000000000005</v>
       </c>
     </row>
-    <row r="464" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="464" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A464" s="2" t="s">
         <v>1057</v>
       </c>
@@ -19597,7 +19596,7 @@
         <v>84.995000000000005</v>
       </c>
     </row>
-    <row r="465" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="465" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A465" s="2" t="s">
         <v>1058</v>
       </c>
@@ -19629,7 +19628,7 @@
         <v>84.995000000000005</v>
       </c>
     </row>
-    <row r="466" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="466" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A466" s="2" t="s">
         <v>1059</v>
       </c>
@@ -19661,7 +19660,7 @@
         <v>84.995000000000005</v>
       </c>
     </row>
-    <row r="467" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="467" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A467" s="2" t="s">
         <v>1060</v>
       </c>
@@ -19693,7 +19692,7 @@
         <v>99.995000000000005</v>
       </c>
     </row>
-    <row r="468" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="468" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A468" s="2" t="s">
         <v>1061</v>
       </c>
@@ -19725,7 +19724,7 @@
         <v>99.995000000000005</v>
       </c>
     </row>
-    <row r="469" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="469" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A469" s="2" t="s">
         <v>1062</v>
       </c>
@@ -19757,7 +19756,7 @@
         <v>99.995000000000005</v>
       </c>
     </row>
-    <row r="470" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="470" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A470" s="2" t="s">
         <v>1063</v>
       </c>
@@ -19789,7 +19788,7 @@
         <v>99.995000000000005</v>
       </c>
     </row>
-    <row r="471" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="471" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A471" s="2" t="s">
         <v>1064</v>
       </c>
@@ -19821,7 +19820,7 @@
         <v>84.995000000000005</v>
       </c>
     </row>
-    <row r="472" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="472" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A472" s="2" t="s">
         <v>1065</v>
       </c>
@@ -19853,7 +19852,7 @@
         <v>84.995000000000005</v>
       </c>
     </row>
-    <row r="473" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="473" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A473" s="2" t="s">
         <v>1066</v>
       </c>
@@ -19885,7 +19884,7 @@
         <v>84.995000000000005</v>
       </c>
     </row>
-    <row r="474" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="474" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A474" s="2" t="s">
         <v>1067</v>
       </c>
@@ -19917,7 +19916,7 @@
         <v>114.995</v>
       </c>
     </row>
-    <row r="475" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="475" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A475" s="2" t="s">
         <v>1068</v>
       </c>
@@ -19949,7 +19948,7 @@
         <v>114.995</v>
       </c>
     </row>
-    <row r="476" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="476" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A476" s="2" t="s">
         <v>1069</v>
       </c>
@@ -19981,7 +19980,7 @@
         <v>99.995000000000005</v>
       </c>
     </row>
-    <row r="477" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="477" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A477" s="2" t="s">
         <v>1070</v>
       </c>
@@ -20013,7 +20012,7 @@
         <v>99.995000000000005</v>
       </c>
     </row>
-    <row r="478" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="478" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A478" s="2" t="s">
         <v>1071</v>
       </c>
@@ -20045,7 +20044,7 @@
         <v>179.995</v>
       </c>
     </row>
-    <row r="479" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="479" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A479" s="2" t="s">
         <v>1072</v>
       </c>
@@ -20077,7 +20076,7 @@
         <v>179.995</v>
       </c>
     </row>
-    <row r="480" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="480" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A480" s="2" t="s">
         <v>1073</v>
       </c>
@@ -20109,7 +20108,7 @@
         <v>99.995000000000005</v>
       </c>
     </row>
-    <row r="481" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="481" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A481" s="2" t="s">
         <v>1074</v>
       </c>
@@ -20141,7 +20140,7 @@
         <v>99.995000000000005</v>
       </c>
     </row>
-    <row r="482" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="482" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A482" s="2" t="s">
         <v>1075</v>
       </c>
@@ -20173,7 +20172,7 @@
         <v>99.995000000000005</v>
       </c>
     </row>
-    <row r="483" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="483" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A483" s="2" t="s">
         <v>1076</v>
       </c>
@@ -20205,7 +20204,7 @@
         <v>99.995000000000005</v>
       </c>
     </row>
-    <row r="484" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="484" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A484" s="2" t="s">
         <v>1077</v>
       </c>
@@ -20237,7 +20236,7 @@
         <v>84.995000000000005</v>
       </c>
     </row>
-    <row r="485" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="485" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A485" s="2" t="s">
         <v>1078</v>
       </c>
@@ -20269,7 +20268,7 @@
         <v>84.995000000000005</v>
       </c>
     </row>
-    <row r="486" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="486" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A486" s="2" t="s">
         <v>1079</v>
       </c>
@@ -20301,7 +20300,7 @@
         <v>84.995000000000005</v>
       </c>
     </row>
-    <row r="487" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="487" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A487" s="2" t="s">
         <v>1080</v>
       </c>
@@ -20333,7 +20332,7 @@
         <v>84.995000000000005</v>
       </c>
     </row>
-    <row r="488" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="488" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A488" s="2" t="s">
         <v>1081</v>
       </c>
@@ -20365,7 +20364,7 @@
         <v>109.995</v>
       </c>
     </row>
-    <row r="489" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="489" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A489" s="2" t="s">
         <v>1082</v>
       </c>
@@ -20397,7 +20396,7 @@
         <v>109.995</v>
       </c>
     </row>
-    <row r="490" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="490" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A490" s="2" t="s">
         <v>1083</v>
       </c>
@@ -20429,7 +20428,7 @@
         <v>109.995</v>
       </c>
     </row>
-    <row r="491" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="491" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A491" s="2" t="s">
         <v>1084</v>
       </c>
@@ -20461,7 +20460,7 @@
         <v>99.995000000000005</v>
       </c>
     </row>
-    <row r="492" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="492" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A492" s="2" t="s">
         <v>1085</v>
       </c>
@@ -20493,7 +20492,7 @@
         <v>179.995</v>
       </c>
     </row>
-    <row r="493" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="493" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A493" s="2" t="s">
         <v>1086</v>
       </c>
@@ -20525,7 +20524,7 @@
         <v>179.995</v>
       </c>
     </row>
-    <row r="494" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="494" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A494" s="2" t="s">
         <v>1087</v>
       </c>
@@ -20557,7 +20556,7 @@
         <v>44.994999999999997</v>
       </c>
     </row>
-    <row r="495" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="495" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A495" s="2" t="s">
         <v>1088</v>
       </c>
@@ -20589,7 +20588,7 @@
         <v>44.994999999999997</v>
       </c>
     </row>
-    <row r="496" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="496" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A496" s="2" t="s">
         <v>1089</v>
       </c>
@@ -20621,7 +20620,7 @@
         <v>59.994999999999997</v>
       </c>
     </row>
-    <row r="497" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="497" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A497" s="2" t="s">
         <v>1090</v>
       </c>
@@ -20653,7 +20652,7 @@
         <v>59.994999999999997</v>
       </c>
     </row>
-    <row r="498" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="498" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A498" s="2" t="s">
         <v>1091</v>
       </c>
@@ -20685,7 +20684,7 @@
         <v>59.994999999999997</v>
       </c>
     </row>
-    <row r="499" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="499" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A499" s="2" t="s">
         <v>1092</v>
       </c>
@@ -20717,7 +20716,7 @@
         <v>59.994999999999997</v>
       </c>
     </row>
-    <row r="500" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="500" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A500" s="2" t="s">
         <v>1093</v>
       </c>
@@ -20749,7 +20748,7 @@
         <v>29.995000000000001</v>
       </c>
     </row>
-    <row r="501" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="501" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A501" s="2" t="s">
         <v>1094</v>
       </c>
@@ -20781,7 +20780,7 @@
         <v>29.995000000000001</v>
       </c>
     </row>
-    <row r="502" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="502" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A502" s="2" t="s">
         <v>1095</v>
       </c>
@@ -20813,7 +20812,7 @@
         <v>29.995000000000001</v>
       </c>
     </row>
-    <row r="503" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="503" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A503" s="2" t="s">
         <v>1096</v>
       </c>
@@ -20845,7 +20844,7 @@
         <v>29.995000000000001</v>
       </c>
     </row>
-    <row r="504" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="504" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A504" s="2" t="s">
         <v>1097</v>
       </c>
@@ -20877,7 +20876,7 @@
         <v>29.995000000000001</v>
       </c>
     </row>
-    <row r="505" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="505" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A505" s="2" t="s">
         <v>1098</v>
       </c>
@@ -20909,7 +20908,7 @@
         <v>29.995000000000001</v>
       </c>
     </row>
-    <row r="506" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="506" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A506" s="2" t="s">
         <v>1099</v>
       </c>
@@ -20941,7 +20940,7 @@
         <v>29.995000000000001</v>
       </c>
     </row>
-    <row r="507" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="507" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A507" s="2" t="s">
         <v>1100</v>
       </c>
@@ -20973,7 +20972,7 @@
         <v>29.995000000000001</v>
       </c>
     </row>
-    <row r="508" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="508" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A508" s="2" t="s">
         <v>1101</v>
       </c>
@@ -21005,7 +21004,7 @@
         <v>29.995000000000001</v>
       </c>
     </row>
-    <row r="509" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="509" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A509" s="2" t="s">
         <v>1102</v>
       </c>
@@ -21037,7 +21036,7 @@
         <v>29.995000000000001</v>
       </c>
     </row>
-    <row r="510" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="510" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A510" s="2" t="s">
         <v>1103</v>
       </c>
@@ -21069,7 +21068,7 @@
         <v>29.995000000000001</v>
       </c>
     </row>
-    <row r="511" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="511" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A511" s="2" t="s">
         <v>1104</v>
       </c>
@@ -21101,7 +21100,7 @@
         <v>29.995000000000001</v>
       </c>
     </row>
-    <row r="512" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="512" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A512" s="2" t="s">
         <v>1105</v>
       </c>
@@ -21133,7 +21132,7 @@
         <v>29.995000000000001</v>
       </c>
     </row>
-    <row r="513" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="513" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A513" s="2" t="s">
         <v>1106</v>
       </c>
@@ -21165,7 +21164,7 @@
         <v>29.995000000000001</v>
       </c>
     </row>
-    <row r="514" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="514" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A514" s="2" t="s">
         <v>1107</v>
       </c>
@@ -21197,7 +21196,7 @@
         <v>89.995000000000005</v>
       </c>
     </row>
-    <row r="515" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="515" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A515" s="2" t="s">
         <v>1108</v>
       </c>
@@ -21229,7 +21228,7 @@
         <v>89.995000000000005</v>
       </c>
     </row>
-    <row r="516" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="516" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A516" s="2" t="s">
         <v>1109</v>
       </c>
@@ -21261,7 +21260,7 @@
         <v>89.995000000000005</v>
       </c>
     </row>
-    <row r="517" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="517" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A517" s="2" t="s">
         <v>1110</v>
       </c>
@@ -21293,7 +21292,7 @@
         <v>124.995</v>
       </c>
     </row>
-    <row r="518" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="518" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A518" s="2" t="s">
         <v>1111</v>
       </c>
@@ -21325,7 +21324,7 @@
         <v>124.995</v>
       </c>
     </row>
-    <row r="519" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="519" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A519" s="2" t="s">
         <v>1112</v>
       </c>
@@ -21357,7 +21356,7 @@
         <v>99.995000000000005</v>
       </c>
     </row>
-    <row r="520" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="520" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A520" s="2" t="s">
         <v>1113</v>
       </c>
@@ -21389,7 +21388,7 @@
         <v>99.995000000000005</v>
       </c>
     </row>
-    <row r="521" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="521" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A521" s="2" t="s">
         <v>1114</v>
       </c>
@@ -21421,7 +21420,7 @@
         <v>74.995000000000005</v>
       </c>
     </row>
-    <row r="522" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="522" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A522" s="2" t="s">
         <v>1115</v>
       </c>
@@ -21453,7 +21452,7 @@
         <v>74.995000000000005</v>
       </c>
     </row>
-    <row r="523" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="523" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A523" s="2" t="s">
         <v>1116</v>
       </c>
@@ -21485,7 +21484,7 @@
         <v>74.995000000000005</v>
       </c>
     </row>
-    <row r="524" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="524" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A524" s="2" t="s">
         <v>1117</v>
       </c>
@@ -21517,7 +21516,7 @@
         <v>74.995000000000005</v>
       </c>
     </row>
-    <row r="525" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="525" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A525" s="2" t="s">
         <v>1118</v>
       </c>
@@ -21549,7 +21548,7 @@
         <v>69.995000000000005</v>
       </c>
     </row>
-    <row r="526" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="526" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A526" s="2" t="s">
         <v>1119</v>
       </c>
@@ -21581,7 +21580,7 @@
         <v>99.995000000000005</v>
       </c>
     </row>
-    <row r="527" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="527" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A527" s="2" t="s">
         <v>1120</v>
       </c>
@@ -21613,7 +21612,7 @@
         <v>64.995000000000005</v>
       </c>
     </row>
-    <row r="528" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="528" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A528" s="2" t="s">
         <v>1121</v>
       </c>
@@ -21645,7 +21644,7 @@
         <v>64.995000000000005</v>
       </c>
     </row>
-    <row r="529" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="529" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A529" s="2" t="s">
         <v>1122</v>
       </c>
@@ -21677,7 +21676,7 @@
         <v>64.995000000000005</v>
       </c>
     </row>
-    <row r="530" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="530" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A530" s="2" t="s">
         <v>1123</v>
       </c>
@@ -21709,7 +21708,7 @@
         <v>59.994999999999997</v>
       </c>
     </row>
-    <row r="531" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="531" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A531" s="2" t="s">
         <v>1124</v>
       </c>
@@ -21741,7 +21740,7 @@
         <v>59.994999999999997</v>
       </c>
     </row>
-    <row r="532" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="532" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A532" s="2" t="s">
         <v>1125</v>
       </c>
@@ -21773,7 +21772,7 @@
         <v>59.994999999999997</v>
       </c>
     </row>
-    <row r="533" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="533" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A533" s="2" t="s">
         <v>1126</v>
       </c>
@@ -21805,7 +21804,7 @@
         <v>59.994999999999997</v>
       </c>
     </row>
-    <row r="534" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="534" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A534" s="2" t="s">
         <v>1127</v>
       </c>
@@ -21837,7 +21836,7 @@
         <v>59.994999999999997</v>
       </c>
     </row>
-    <row r="535" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="535" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A535" s="2" t="s">
         <v>1128</v>
       </c>
@@ -21869,7 +21868,7 @@
         <v>59.994999999999997</v>
       </c>
     </row>
-    <row r="536" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="536" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A536" s="2" t="s">
         <v>1129</v>
       </c>
@@ -21901,7 +21900,7 @@
         <v>54.994999999999997</v>
       </c>
     </row>
-    <row r="537" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="537" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A537" s="2" t="s">
         <v>1130</v>
       </c>
@@ -21933,7 +21932,7 @@
         <v>54.994999999999997</v>
       </c>
     </row>
-    <row r="538" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="538" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A538" s="2" t="s">
         <v>1131</v>
       </c>
@@ -21965,7 +21964,7 @@
         <v>54.994999999999997</v>
       </c>
     </row>
-    <row r="539" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="539" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A539" s="2" t="s">
         <v>1132</v>
       </c>
@@ -21997,7 +21996,7 @@
         <v>54.994999999999997</v>
       </c>
     </row>
-    <row r="540" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="540" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A540" s="2" t="s">
         <v>1133</v>
       </c>
@@ -22029,7 +22028,7 @@
         <v>54.994999999999997</v>
       </c>
     </row>
-    <row r="541" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="541" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A541" s="2" t="s">
         <v>1134</v>
       </c>
@@ -22061,7 +22060,7 @@
         <v>59.994999999999997</v>
       </c>
     </row>
-    <row r="542" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="542" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A542" s="2" t="s">
         <v>1135</v>
       </c>
@@ -22093,7 +22092,7 @@
         <v>89.995000000000005</v>
       </c>
     </row>
-    <row r="543" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="543" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A543" s="2" t="s">
         <v>1136</v>
       </c>
@@ -22125,7 +22124,7 @@
         <v>74.995000000000005</v>
       </c>
     </row>
-    <row r="544" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="544" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A544" s="2" t="s">
         <v>1137</v>
       </c>
@@ -22157,7 +22156,7 @@
         <v>74.995000000000005</v>
       </c>
     </row>
-    <row r="545" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="545" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A545" s="2" t="s">
         <v>1138</v>
       </c>
@@ -22189,7 +22188,7 @@
         <v>74.995000000000005</v>
       </c>
     </row>
-    <row r="546" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="546" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A546" s="2" t="s">
         <v>1139</v>
       </c>
@@ -22221,7 +22220,7 @@
         <v>74.995000000000005</v>
       </c>
     </row>
-    <row r="547" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="547" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A547" s="2" t="s">
         <v>1140</v>
       </c>
@@ -22253,7 +22252,7 @@
         <v>99.995000000000005</v>
       </c>
     </row>
-    <row r="548" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="548" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A548" s="2" t="s">
         <v>1141</v>
       </c>
@@ -22285,7 +22284,7 @@
         <v>99.995000000000005</v>
       </c>
     </row>
-    <row r="549" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="549" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A549" s="2" t="s">
         <v>1142</v>
       </c>
@@ -22317,7 +22316,7 @@
         <v>124.995</v>
       </c>
     </row>
-    <row r="550" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="550" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A550" s="2" t="s">
         <v>1143</v>
       </c>
@@ -22349,7 +22348,7 @@
         <v>89.995000000000005</v>
       </c>
     </row>
-    <row r="551" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="551" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A551" s="2" t="s">
         <v>1144</v>
       </c>
@@ -22381,7 +22380,7 @@
         <v>99.995000000000005</v>
       </c>
     </row>
-    <row r="552" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="552" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A552" s="2" t="s">
         <v>1145</v>
       </c>
@@ -22413,7 +22412,7 @@
         <v>64.995000000000005</v>
       </c>
     </row>
-    <row r="553" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="553" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A553" s="2" t="s">
         <v>1146</v>
       </c>
@@ -22445,7 +22444,7 @@
         <v>64.995000000000005</v>
       </c>
     </row>
-    <row r="554" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="554" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A554" s="2" t="s">
         <v>1147</v>
       </c>
@@ -22477,7 +22476,7 @@
         <v>59.994999999999997</v>
       </c>
     </row>
-    <row r="555" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="555" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A555" s="2" t="s">
         <v>1148</v>
       </c>
@@ -22509,7 +22508,7 @@
         <v>59.994999999999997</v>
       </c>
     </row>
-    <row r="556" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="556" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A556" s="2" t="s">
         <v>1149</v>
       </c>
@@ -22541,7 +22540,7 @@
         <v>59.994999999999997</v>
       </c>
     </row>
-    <row r="557" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="557" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A557" s="2" t="s">
         <v>1150</v>
       </c>
@@ -22573,7 +22572,7 @@
         <v>59.994999999999997</v>
       </c>
     </row>
-    <row r="558" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="558" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A558" s="2" t="s">
         <v>1151</v>
       </c>
@@ -22605,7 +22604,7 @@
         <v>54.994999999999997</v>
       </c>
     </row>
-    <row r="559" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="559" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A559" s="2" t="s">
         <v>1152</v>
       </c>
@@ -22637,7 +22636,7 @@
         <v>54.994999999999997</v>
       </c>
     </row>
-    <row r="560" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="560" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A560" s="2" t="s">
         <v>1153</v>
       </c>
@@ -22669,7 +22668,7 @@
         <v>54.994999999999997</v>
       </c>
     </row>
-    <row r="561" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="561" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A561" s="2" t="s">
         <v>1154</v>
       </c>
@@ -22701,7 +22700,7 @@
         <v>54.994999999999997</v>
       </c>
     </row>
-    <row r="562" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="562" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A562" s="2" t="s">
         <v>1155</v>
       </c>
@@ -22733,7 +22732,7 @@
         <v>99.995000000000005</v>
       </c>
     </row>
-    <row r="563" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="563" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A563" s="2" t="s">
         <v>1156</v>
       </c>
@@ -22765,7 +22764,7 @@
         <v>49.994999999999997</v>
       </c>
     </row>
-    <row r="564" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="564" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A564" s="2" t="s">
         <v>1157</v>
       </c>
@@ -22797,7 +22796,7 @@
         <v>49.994999999999997</v>
       </c>
     </row>
-    <row r="565" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="565" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A565" s="2" t="s">
         <v>1158</v>
       </c>
@@ -22829,7 +22828,7 @@
         <v>49.994999999999997</v>
       </c>
     </row>
-    <row r="566" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="566" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A566" s="2" t="s">
         <v>1159</v>
       </c>
@@ -22861,7 +22860,7 @@
         <v>49.994999999999997</v>
       </c>
     </row>
-    <row r="567" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="567" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A567" s="2" t="s">
         <v>1160</v>
       </c>
@@ -22893,7 +22892,7 @@
         <v>49.994999999999997</v>
       </c>
     </row>
-    <row r="568" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="568" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A568" s="2" t="s">
         <v>1161</v>
       </c>
@@ -22925,7 +22924,7 @@
         <v>49.994999999999997</v>
       </c>
     </row>
-    <row r="569" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="569" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A569" s="2" t="s">
         <v>1162</v>
       </c>
@@ -22957,7 +22956,7 @@
         <v>49.994999999999997</v>
       </c>
     </row>
-    <row r="570" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="570" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A570" s="2" t="s">
         <v>1163</v>
       </c>
@@ -22989,7 +22988,7 @@
         <v>44.994999999999997</v>
       </c>
     </row>
-    <row r="571" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="571" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A571" s="2" t="s">
         <v>1164</v>
       </c>
@@ -23021,7 +23020,7 @@
         <v>44.994999999999997</v>
       </c>
     </row>
-    <row r="572" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="572" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A572" s="2" t="s">
         <v>1165</v>
       </c>
@@ -23053,7 +23052,7 @@
         <v>44.994999999999997</v>
       </c>
     </row>
-    <row r="573" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="573" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A573" s="2" t="s">
         <v>1166</v>
       </c>
@@ -23085,7 +23084,7 @@
         <v>34.994999999999997</v>
       </c>
     </row>
-    <row r="574" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="574" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A574" s="2" t="s">
         <v>1167</v>
       </c>
@@ -23117,7 +23116,7 @@
         <v>34.994999999999997</v>
       </c>
     </row>
-    <row r="575" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="575" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A575" s="2" t="s">
         <v>1168</v>
       </c>
@@ -23149,7 +23148,7 @@
         <v>29.995000000000001</v>
       </c>
     </row>
-    <row r="576" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="576" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A576" s="2" t="s">
         <v>1169</v>
       </c>
@@ -23181,7 +23180,7 @@
         <v>29.995000000000001</v>
       </c>
     </row>
-    <row r="577" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="577" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A577" s="2" t="s">
         <v>1170</v>
       </c>
@@ -23213,7 +23212,7 @@
         <v>29.995000000000001</v>
       </c>
     </row>
-    <row r="578" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="578" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A578" s="2" t="s">
         <v>1171</v>
       </c>
@@ -23245,7 +23244,7 @@
         <v>29.995000000000001</v>
       </c>
     </row>
-    <row r="579" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="579" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A579" s="2" t="s">
         <v>1172</v>
       </c>
@@ -23277,7 +23276,7 @@
         <v>29.995000000000001</v>
       </c>
     </row>
-    <row r="580" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="580" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A580" s="2" t="s">
         <v>1173</v>
       </c>
@@ -23309,7 +23308,7 @@
         <v>29.995000000000001</v>
       </c>
     </row>
-    <row r="581" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="581" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A581" s="2" t="s">
         <v>1174</v>
       </c>
@@ -23341,7 +23340,7 @@
         <v>29.995000000000001</v>
       </c>
     </row>
-    <row r="582" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="582" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A582" s="2" t="s">
         <v>1175</v>
       </c>
@@ -23373,7 +23372,7 @@
         <v>29.995000000000001</v>
       </c>
     </row>
-    <row r="583" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="583" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A583" s="2" t="s">
         <v>1176</v>
       </c>
@@ -23405,7 +23404,7 @@
         <v>29.995000000000001</v>
       </c>
     </row>
-    <row r="584" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="584" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A584" s="2" t="s">
         <v>1177</v>
       </c>
@@ -23437,7 +23436,7 @@
         <v>29.995000000000001</v>
       </c>
     </row>
-    <row r="585" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="585" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A585" s="2" t="s">
         <v>1178</v>
       </c>
@@ -23469,7 +23468,7 @@
         <v>29.995000000000001</v>
       </c>
     </row>
-    <row r="586" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="586" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A586" s="2" t="s">
         <v>1179</v>
       </c>
@@ -23501,7 +23500,7 @@
         <v>29.995000000000001</v>
       </c>
     </row>
-    <row r="587" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="587" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A587" s="2" t="s">
         <v>1180</v>
       </c>
@@ -23533,7 +23532,7 @@
         <v>29.995000000000001</v>
       </c>
     </row>
-    <row r="588" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="588" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A588" s="2" t="s">
         <v>1181</v>
       </c>
@@ -23565,7 +23564,7 @@
         <v>29.995000000000001</v>
       </c>
     </row>
-    <row r="589" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="589" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A589" s="2" t="s">
         <v>1182</v>
       </c>
@@ -23597,7 +23596,7 @@
         <v>29.995000000000001</v>
       </c>
     </row>
-    <row r="590" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="590" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A590" s="2" t="s">
         <v>1183</v>
       </c>
@@ -23629,7 +23628,7 @@
         <v>29.995000000000001</v>
       </c>
     </row>
-    <row r="591" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="591" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A591" s="2" t="s">
         <v>1184</v>
       </c>
@@ -23661,7 +23660,7 @@
         <v>29.995000000000001</v>
       </c>
     </row>
-    <row r="592" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="592" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A592" s="2" t="s">
         <v>1185</v>
       </c>
@@ -23693,7 +23692,7 @@
         <v>32.494999999999997</v>
       </c>
     </row>
-    <row r="593" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="593" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A593" s="2" t="s">
         <v>1186</v>
       </c>
@@ -23725,7 +23724,7 @@
         <v>32.494999999999997</v>
       </c>
     </row>
-    <row r="594" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="594" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A594" s="2" t="s">
         <v>1187</v>
       </c>
@@ -23757,7 +23756,7 @@
         <v>32.494999999999997</v>
       </c>
     </row>
-    <row r="595" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="595" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A595" s="2" t="s">
         <v>1188</v>
       </c>
@@ -23789,7 +23788,7 @@
         <v>34.994999999999997</v>
       </c>
     </row>
-    <row r="596" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="596" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A596" s="2" t="s">
         <v>1189</v>
       </c>
@@ -23821,7 +23820,7 @@
         <v>34.994999999999997</v>
       </c>
     </row>
-    <row r="597" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="597" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A597" s="2" t="s">
         <v>1190</v>
       </c>
@@ -23853,7 +23852,7 @@
         <v>29.995000000000001</v>
       </c>
     </row>
-    <row r="598" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="598" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A598" s="2" t="s">
         <v>1191</v>
       </c>
@@ -23885,7 +23884,7 @@
         <v>29.995000000000001</v>
       </c>
     </row>
-    <row r="599" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="599" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A599" s="2" t="s">
         <v>1192</v>
       </c>
@@ -23917,7 +23916,7 @@
         <v>29.995000000000001</v>
       </c>
     </row>
-    <row r="600" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="600" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A600" s="2" t="s">
         <v>1193</v>
       </c>
@@ -23949,7 +23948,7 @@
         <v>29.995000000000001</v>
       </c>
     </row>
-    <row r="601" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="601" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A601" s="2" t="s">
         <v>1194</v>
       </c>
@@ -23981,7 +23980,7 @@
         <v>29.995000000000001</v>
       </c>
     </row>
-    <row r="602" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="602" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A602" s="2" t="s">
         <v>1195</v>
       </c>
@@ -24013,7 +24012,7 @@
         <v>29.995000000000001</v>
       </c>
     </row>
-    <row r="603" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="603" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A603" s="2" t="s">
         <v>1196</v>
       </c>
@@ -24045,7 +24044,7 @@
         <v>29.995000000000001</v>
       </c>
     </row>
-    <row r="604" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="604" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A604" s="2" t="s">
         <v>1197</v>
       </c>
@@ -24077,7 +24076,7 @@
         <v>29.995000000000001</v>
       </c>
     </row>
-    <row r="605" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="605" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A605" s="2" t="s">
         <v>1198</v>
       </c>
@@ -24109,7 +24108,7 @@
         <v>29.995000000000001</v>
       </c>
     </row>
-    <row r="606" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="606" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A606" s="2" t="s">
         <v>1199</v>
       </c>
@@ -24141,7 +24140,7 @@
         <v>29.995000000000001</v>
       </c>
     </row>
-    <row r="607" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="607" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A607" s="2" t="s">
         <v>1200</v>
       </c>
@@ -24173,7 +24172,7 @@
         <v>29.995000000000001</v>
       </c>
     </row>
-    <row r="608" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="608" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A608" s="2" t="s">
         <v>1201</v>
       </c>
@@ -24205,7 +24204,7 @@
         <v>29.995000000000001</v>
       </c>
     </row>
-    <row r="609" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="609" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A609" s="2" t="s">
         <v>1202</v>
       </c>
@@ -24237,7 +24236,7 @@
         <v>29.995000000000001</v>
       </c>
     </row>
-    <row r="610" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="610" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A610" s="2" t="s">
         <v>1203</v>
       </c>
@@ -24269,7 +24268,7 @@
         <v>29.995000000000001</v>
       </c>
     </row>
-    <row r="611" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="611" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A611" s="2" t="s">
         <v>1204</v>
       </c>
@@ -24301,7 +24300,7 @@
         <v>29.995000000000001</v>
       </c>
     </row>
-    <row r="612" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="612" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A612" s="2" t="s">
         <v>1205</v>
       </c>
@@ -24333,7 +24332,7 @@
         <v>29.995000000000001</v>
       </c>
     </row>
-    <row r="613" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="613" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A613" s="2" t="s">
         <v>1206</v>
       </c>
@@ -24365,7 +24364,7 @@
         <v>32.494999999999997</v>
       </c>
     </row>
-    <row r="614" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="614" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A614" s="2" t="s">
         <v>1207</v>
       </c>
@@ -24397,7 +24396,7 @@
         <v>32.494999999999997</v>
       </c>
     </row>
-    <row r="615" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="615" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A615" s="2" t="s">
         <v>1208</v>
       </c>
@@ -24429,7 +24428,7 @@
         <v>32.494999999999997</v>
       </c>
     </row>
-    <row r="616" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="616" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A616" s="2" t="s">
         <v>1209</v>
       </c>
@@ -24461,7 +24460,7 @@
         <v>32.494999999999997</v>
       </c>
     </row>
-    <row r="617" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="617" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A617" s="2" t="s">
         <v>1210</v>
       </c>
@@ -24493,7 +24492,7 @@
         <v>49.994999999999997</v>
       </c>
     </row>
-    <row r="618" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="618" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A618" s="2" t="s">
         <v>1211</v>
       </c>
@@ -24525,7 +24524,7 @@
         <v>69.995000000000005</v>
       </c>
     </row>
-    <row r="619" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="619" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A619" s="2" t="s">
         <v>1212</v>
       </c>
@@ -24557,7 +24556,7 @@
         <v>64.995000000000005</v>
       </c>
     </row>
-    <row r="620" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="620" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A620" s="2" t="s">
         <v>1213</v>
       </c>
@@ -24589,7 +24588,7 @@
         <v>64.995000000000005</v>
       </c>
     </row>
-    <row r="621" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="621" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A621" s="2" t="s">
         <v>1214</v>
       </c>
@@ -24621,7 +24620,7 @@
         <v>74.995000000000005</v>
       </c>
     </row>
-    <row r="622" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="622" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A622" s="2" t="s">
         <v>1215</v>
       </c>
@@ -24653,7 +24652,7 @@
         <v>69.995000000000005</v>
       </c>
     </row>
-    <row r="623" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="623" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A623" s="2" t="s">
         <v>1216</v>
       </c>
@@ -24685,7 +24684,7 @@
         <v>69.995000000000005</v>
       </c>
     </row>
-    <row r="624" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="624" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A624" s="2" t="s">
         <v>1217</v>
       </c>
@@ -24717,7 +24716,7 @@
         <v>69.995000000000005</v>
       </c>
     </row>
-    <row r="625" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="625" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A625" s="2" t="s">
         <v>1218</v>
       </c>
@@ -24749,7 +24748,7 @@
         <v>69.995000000000005</v>
       </c>
     </row>
-    <row r="626" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="626" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A626" s="2" t="s">
         <v>1219</v>
       </c>
@@ -24781,7 +24780,7 @@
         <v>69.995000000000005</v>
       </c>
     </row>
-    <row r="627" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="627" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A627" s="2" t="s">
         <v>1220</v>
       </c>
@@ -24813,7 +24812,7 @@
         <v>49.994999999999997</v>
       </c>
     </row>
-    <row r="628" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="628" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A628" s="2" t="s">
         <v>1221</v>
       </c>
@@ -24845,7 +24844,7 @@
         <v>49.994999999999997</v>
       </c>
     </row>
-    <row r="629" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="629" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A629" s="2" t="s">
         <v>1222</v>
       </c>
@@ -24877,7 +24876,7 @@
         <v>49.994999999999997</v>
       </c>
     </row>
-    <row r="630" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="630" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A630" s="2" t="s">
         <v>1223</v>
       </c>
@@ -24909,7 +24908,7 @@
         <v>49.994999999999997</v>
       </c>
     </row>
-    <row r="631" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="631" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A631" s="2" t="s">
         <v>1224</v>
       </c>
@@ -24941,7 +24940,7 @@
         <v>49.994999999999997</v>
       </c>
     </row>
-    <row r="632" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="632" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A632" s="2" t="s">
         <v>1225</v>
       </c>
@@ -24973,7 +24972,7 @@
         <v>49.994999999999997</v>
       </c>
     </row>
-    <row r="633" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="633" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A633" s="2" t="s">
         <v>1226</v>
       </c>
@@ -25005,7 +25004,7 @@
         <v>49.994999999999997</v>
       </c>
     </row>
-    <row r="634" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="634" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A634" s="2" t="s">
         <v>1227</v>
       </c>
@@ -25037,7 +25036,7 @@
         <v>49.994999999999997</v>
       </c>
     </row>
-    <row r="635" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="635" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A635" s="2" t="s">
         <v>1228</v>
       </c>
@@ -25069,7 +25068,7 @@
         <v>49.994999999999997</v>
       </c>
     </row>
-    <row r="636" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="636" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A636" s="2" t="s">
         <v>1229</v>
       </c>
@@ -25101,7 +25100,7 @@
         <v>44.994999999999997</v>
       </c>
     </row>
-    <row r="637" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="637" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A637" s="2" t="s">
         <v>1230</v>
       </c>
@@ -25133,7 +25132,7 @@
         <v>44.994999999999997</v>
       </c>
     </row>
-    <row r="638" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="638" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A638" s="2" t="s">
         <v>1231</v>
       </c>
@@ -25165,7 +25164,7 @@
         <v>44.994999999999997</v>
       </c>
     </row>
-    <row r="639" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="639" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A639" s="2" t="s">
         <v>1232</v>
       </c>
@@ -25197,7 +25196,7 @@
         <v>44.994999999999997</v>
       </c>
     </row>
-    <row r="640" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="640" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A640" s="2" t="s">
         <v>1233</v>
       </c>
@@ -25229,7 +25228,7 @@
         <v>44.994999999999997</v>
       </c>
     </row>
-    <row r="641" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="641" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A641" s="2" t="s">
         <v>1234</v>
       </c>
@@ -25261,7 +25260,7 @@
         <v>44.994999999999997</v>
       </c>
     </row>
-    <row r="642" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="642" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A642" s="2" t="s">
         <v>1235</v>
       </c>
@@ -25293,7 +25292,7 @@
         <v>44.994999999999997</v>
       </c>
     </row>
-    <row r="643" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="643" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A643" s="2" t="s">
         <v>1236</v>
       </c>
@@ -25325,7 +25324,7 @@
         <v>39.994999999999997</v>
       </c>
     </row>
-    <row r="644" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="644" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A644" s="2" t="s">
         <v>1237</v>
       </c>
@@ -25357,7 +25356,7 @@
         <v>39.994999999999997</v>
       </c>
     </row>
-    <row r="645" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="645" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A645" s="2" t="s">
         <v>1238</v>
       </c>
@@ -25389,7 +25388,7 @@
         <v>39.994999999999997</v>
       </c>
     </row>
-    <row r="646" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="646" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A646" s="2" t="s">
         <v>1239</v>
       </c>
@@ -25421,7 +25420,7 @@
         <v>39.994999999999997</v>
       </c>
     </row>
-    <row r="647" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="647" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A647" s="2" t="s">
         <v>1240</v>
       </c>
@@ -25453,7 +25452,7 @@
         <v>39.994999999999997</v>
       </c>
     </row>
-    <row r="648" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="648" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A648" s="2" t="s">
         <v>1241</v>
       </c>
@@ -25485,7 +25484,7 @@
         <v>39.994999999999997</v>
       </c>
     </row>
-    <row r="649" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="649" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A649" s="2" t="s">
         <v>1242</v>
       </c>
@@ -25517,7 +25516,7 @@
         <v>39.994999999999997</v>
       </c>
     </row>
-    <row r="650" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="650" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A650" s="2" t="s">
         <v>1243</v>
       </c>
@@ -25549,7 +25548,7 @@
         <v>49.994999999999997</v>
       </c>
     </row>
-    <row r="651" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="651" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A651" s="2" t="s">
         <v>1244</v>
       </c>
@@ -25581,7 +25580,7 @@
         <v>49.994999999999997</v>
       </c>
     </row>
-    <row r="652" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="652" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A652" s="2" t="s">
         <v>1245</v>
       </c>
@@ -25613,7 +25612,7 @@
         <v>49.994999999999997</v>
       </c>
     </row>
-    <row r="653" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="653" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A653" s="2" t="s">
         <v>1246</v>
       </c>
@@ -25645,7 +25644,7 @@
         <v>49.994999999999997</v>
       </c>
     </row>
-    <row r="654" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="654" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A654" s="2" t="s">
         <v>1247</v>
       </c>
@@ -25677,7 +25676,7 @@
         <v>79.995000000000005</v>
       </c>
     </row>
-    <row r="655" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="655" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A655" s="2" t="s">
         <v>1248</v>
       </c>
@@ -25709,7 +25708,7 @@
         <v>79.995000000000005</v>
       </c>
     </row>
-    <row r="656" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="656" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A656" s="2" t="s">
         <v>1249</v>
       </c>
@@ -25741,7 +25740,7 @@
         <v>79.995000000000005</v>
       </c>
     </row>
-    <row r="657" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="657" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A657" s="2" t="s">
         <v>1250</v>
       </c>
@@ -25773,7 +25772,7 @@
         <v>79.995000000000005</v>
       </c>
     </row>
-    <row r="658" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="658" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A658" s="2" t="s">
         <v>1251</v>
       </c>
@@ -25805,7 +25804,7 @@
         <v>69.995000000000005</v>
       </c>
     </row>
-    <row r="659" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="659" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A659" s="2" t="s">
         <v>1252</v>
       </c>
@@ -25837,7 +25836,7 @@
         <v>69.995000000000005</v>
       </c>
     </row>
-    <row r="660" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="660" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A660" s="2" t="s">
         <v>1253</v>
       </c>
@@ -25869,7 +25868,7 @@
         <v>74.995000000000005</v>
       </c>
     </row>
-    <row r="661" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="661" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A661" s="2" t="s">
         <v>1254</v>
       </c>
@@ -25901,7 +25900,7 @@
         <v>74.995000000000005</v>
       </c>
     </row>
-    <row r="662" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="662" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A662" s="2" t="s">
         <v>1255</v>
       </c>
@@ -25933,7 +25932,7 @@
         <v>64.995000000000005</v>
       </c>
     </row>
-    <row r="663" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="663" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A663" s="2" t="s">
         <v>1256</v>
       </c>
@@ -25965,7 +25964,7 @@
         <v>64.995000000000005</v>
       </c>
     </row>
-    <row r="664" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="664" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A664" s="2" t="s">
         <v>1257</v>
       </c>
@@ -25997,7 +25996,7 @@
         <v>99.995000000000005</v>
       </c>
     </row>
-    <row r="665" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="665" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A665" s="2" t="s">
         <v>1258</v>
       </c>
@@ -26029,7 +26028,7 @@
         <v>99.995000000000005</v>
       </c>
     </row>
-    <row r="666" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="666" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A666" s="2" t="s">
         <v>1259</v>
       </c>
@@ -26061,7 +26060,7 @@
         <v>144.995</v>
       </c>
     </row>
-    <row r="667" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="667" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A667" s="2" t="s">
         <v>1260</v>
       </c>
@@ -26093,7 +26092,7 @@
         <v>144.995</v>
       </c>
     </row>
-    <row r="668" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="668" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A668" s="2" t="s">
         <v>1261</v>
       </c>
@@ -26125,7 +26124,7 @@
         <v>44.994999999999997</v>
       </c>
     </row>
-    <row r="669" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="669" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A669" s="2" t="s">
         <v>1262</v>
       </c>
@@ -26157,7 +26156,7 @@
         <v>44.994999999999997</v>
       </c>
     </row>
-    <row r="670" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="670" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A670" s="2" t="s">
         <v>1263</v>
       </c>
@@ -26189,7 +26188,7 @@
         <v>44.994999999999997</v>
       </c>
     </row>
-    <row r="671" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="671" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A671" s="2" t="s">
         <v>1264</v>
       </c>
@@ -26221,7 +26220,7 @@
         <v>44.994999999999997</v>
       </c>
     </row>
-    <row r="672" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="672" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A672" s="2" t="s">
         <v>1265</v>
       </c>
@@ -26253,7 +26252,7 @@
         <v>44.994999999999997</v>
       </c>
     </row>
-    <row r="673" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="673" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A673" s="2" t="s">
         <v>1266</v>
       </c>
@@ -26285,7 +26284,7 @@
         <v>44.994999999999997</v>
       </c>
     </row>
-    <row r="674" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="674" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A674" s="2" t="s">
         <v>1267</v>
       </c>
@@ -26317,7 +26316,7 @@
         <v>44.994999999999997</v>
       </c>
     </row>
-    <row r="675" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="675" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A675" s="2" t="s">
         <v>1268</v>
       </c>
@@ -26349,7 +26348,7 @@
         <v>54.994999999999997</v>
       </c>
     </row>
-    <row r="676" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="676" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A676" s="2" t="s">
         <v>1269</v>
       </c>
@@ -26381,7 +26380,7 @@
         <v>54.994999999999997</v>
       </c>
     </row>
-    <row r="677" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="677" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A677" s="2" t="s">
         <v>1270</v>
       </c>
@@ -26413,7 +26412,7 @@
         <v>54.994999999999997</v>
       </c>
     </row>
-    <row r="678" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="678" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A678" s="2" t="s">
         <v>1271</v>
       </c>
@@ -26445,7 +26444,7 @@
         <v>49.994999999999997</v>
       </c>
     </row>
-    <row r="679" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="679" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A679" s="2" t="s">
         <v>1272</v>
       </c>
@@ -26477,7 +26476,7 @@
         <v>49.994999999999997</v>
       </c>
     </row>
-    <row r="680" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="680" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A680" s="2" t="s">
         <v>1273</v>
       </c>
@@ -26509,7 +26508,7 @@
         <v>49.994999999999997</v>
       </c>
     </row>
-    <row r="681" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="681" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A681" s="2" t="s">
         <v>1274</v>
       </c>
@@ -26541,7 +26540,7 @@
         <v>49.994999999999997</v>
       </c>
     </row>
-    <row r="682" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="682" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A682" s="2" t="s">
         <v>1275</v>
       </c>
@@ -26573,7 +26572,7 @@
         <v>49.994999999999997</v>
       </c>
     </row>
-    <row r="683" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="683" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A683" s="2" t="s">
         <v>1276</v>
       </c>
@@ -26605,7 +26604,7 @@
         <v>49.994999999999997</v>
       </c>
     </row>
-    <row r="684" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="684" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A684" s="2" t="s">
         <v>1277</v>
       </c>
@@ -26637,7 +26636,7 @@
         <v>49.994999999999997</v>
       </c>
     </row>
-    <row r="685" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="685" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A685" s="2" t="s">
         <v>1278</v>
       </c>
@@ -26669,7 +26668,7 @@
         <v>49.994999999999997</v>
       </c>
     </row>
-    <row r="686" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="686" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A686" s="2" t="s">
         <v>1279</v>
       </c>
@@ -26701,7 +26700,7 @@
         <v>49.994999999999997</v>
       </c>
     </row>
-    <row r="687" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="687" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A687" s="2" t="s">
         <v>1280</v>
       </c>
@@ -26733,7 +26732,7 @@
         <v>49.994999999999997</v>
       </c>
     </row>
-    <row r="688" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="688" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A688" s="2" t="s">
         <v>1281</v>
       </c>
@@ -26765,7 +26764,7 @@
         <v>49.994999999999997</v>
       </c>
     </row>
-    <row r="689" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="689" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A689" s="2" t="s">
         <v>1282</v>
       </c>
@@ -26797,7 +26796,7 @@
         <v>49.994999999999997</v>
       </c>
     </row>
-    <row r="690" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="690" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A690" s="2" t="s">
         <v>1283</v>
       </c>
@@ -26829,7 +26828,7 @@
         <v>49.994999999999997</v>
       </c>
     </row>
-    <row r="691" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="691" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A691" s="2" t="s">
         <v>1284</v>
       </c>
@@ -26861,7 +26860,7 @@
         <v>44.994999999999997</v>
       </c>
     </row>
-    <row r="692" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="692" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A692" s="2" t="s">
         <v>1285</v>
       </c>
@@ -26893,7 +26892,7 @@
         <v>44.994999999999997</v>
       </c>
     </row>
-    <row r="693" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="693" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A693" s="2" t="s">
         <v>1286</v>
       </c>
@@ -26925,7 +26924,7 @@
         <v>44.994999999999997</v>
       </c>
     </row>
-    <row r="694" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="694" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A694" s="2" t="s">
         <v>1287</v>
       </c>
@@ -26957,7 +26956,7 @@
         <v>44.994999999999997</v>
       </c>
     </row>
-    <row r="695" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="695" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A695" s="2" t="s">
         <v>1288</v>
       </c>
@@ -26989,7 +26988,7 @@
         <v>44.994999999999997</v>
       </c>
     </row>
-    <row r="696" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="696" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A696" s="2" t="s">
         <v>1289</v>
       </c>
@@ -27021,7 +27020,7 @@
         <v>44.994999999999997</v>
       </c>
     </row>
-    <row r="697" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="697" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A697" s="2" t="s">
         <v>1290</v>
       </c>
@@ -27053,7 +27052,7 @@
         <v>44.994999999999997</v>
       </c>
     </row>
-    <row r="698" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="698" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A698" s="2" t="s">
         <v>1291</v>
       </c>
@@ -27085,7 +27084,7 @@
         <v>44.994999999999997</v>
       </c>
     </row>
-    <row r="699" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="699" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A699" s="2" t="s">
         <v>1292</v>
       </c>
@@ -27117,7 +27116,7 @@
         <v>44.994999999999997</v>
       </c>
     </row>
-    <row r="700" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="700" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A700" s="2" t="s">
         <v>1293</v>
       </c>
@@ -27149,7 +27148,7 @@
         <v>44.994999999999997</v>
       </c>
     </row>
-    <row r="701" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="701" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A701" s="2" t="s">
         <v>1294</v>
       </c>
@@ -27181,7 +27180,7 @@
         <v>44.994999999999997</v>
       </c>
     </row>
-    <row r="702" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="702" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A702" s="2" t="s">
         <v>1295</v>
       </c>
@@ -27213,7 +27212,7 @@
         <v>44.994999999999997</v>
       </c>
     </row>
-    <row r="703" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="703" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A703" s="2" t="s">
         <v>1296</v>
       </c>
@@ -27245,7 +27244,7 @@
         <v>39.994999999999997</v>
       </c>
     </row>
-    <row r="704" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="704" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A704" s="2" t="s">
         <v>1297</v>
       </c>
@@ -27277,7 +27276,7 @@
         <v>39.994999999999997</v>
       </c>
     </row>
-    <row r="705" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="705" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A705" s="2" t="s">
         <v>1298</v>
       </c>
@@ -27309,7 +27308,7 @@
         <v>39.994999999999997</v>
       </c>
     </row>
-    <row r="706" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="706" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A706" s="2" t="s">
         <v>1299</v>
       </c>
@@ -27341,7 +27340,7 @@
         <v>39.994999999999997</v>
       </c>
     </row>
-    <row r="707" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="707" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A707" s="2" t="s">
         <v>1300</v>
       </c>
@@ -27373,7 +27372,7 @@
         <v>39.994999999999997</v>
       </c>
     </row>
-    <row r="708" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="708" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A708" s="2" t="s">
         <v>1301</v>
       </c>
@@ -27405,7 +27404,7 @@
         <v>39.994999999999997</v>
       </c>
     </row>
-    <row r="709" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="709" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A709" s="2" t="s">
         <v>1302</v>
       </c>
@@ -27437,7 +27436,7 @@
         <v>89.995000000000005</v>
       </c>
     </row>
-    <row r="710" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="710" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A710" s="2" t="s">
         <v>1303</v>
       </c>
@@ -27469,7 +27468,7 @@
         <v>89.995000000000005</v>
       </c>
     </row>
-    <row r="711" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="711" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A711" s="2" t="s">
         <v>1304</v>
       </c>
@@ -27501,7 +27500,7 @@
         <v>89.995000000000005</v>
       </c>
     </row>
-    <row r="712" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="712" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A712" s="2" t="s">
         <v>1305</v>
       </c>
@@ -27533,7 +27532,7 @@
         <v>89.995000000000005</v>
       </c>
     </row>
-    <row r="713" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="713" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A713" s="2" t="s">
         <v>1306</v>
       </c>
@@ -27565,7 +27564,7 @@
         <v>59.994999999999997</v>
       </c>
     </row>
-    <row r="714" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="714" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A714" s="2" t="s">
         <v>1307</v>
       </c>
@@ -27597,7 +27596,7 @@
         <v>59.994999999999997</v>
       </c>
     </row>
-    <row r="715" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="715" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A715" s="2" t="s">
         <v>1308</v>
       </c>
@@ -27629,7 +27628,7 @@
         <v>59.994999999999997</v>
       </c>
     </row>
-    <row r="716" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="716" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A716" s="2" t="s">
         <v>1309</v>
       </c>
@@ -27661,7 +27660,7 @@
         <v>59.994999999999997</v>
       </c>
     </row>
-    <row r="717" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="717" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A717" s="2" t="s">
         <v>1310</v>
       </c>
@@ -27693,7 +27692,7 @@
         <v>59.994999999999997</v>
       </c>
     </row>
-    <row r="718" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="718" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A718" s="2" t="s">
         <v>1311</v>
       </c>
@@ -27725,7 +27724,7 @@
         <v>59.994999999999997</v>
       </c>
     </row>
-    <row r="719" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="719" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A719" s="2" t="s">
         <v>1312</v>
       </c>
@@ -27757,7 +27756,7 @@
         <v>54.994999999999997</v>
       </c>
     </row>
-    <row r="720" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="720" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A720" s="2" t="s">
         <v>1313</v>
       </c>
@@ -27789,7 +27788,7 @@
         <v>54.994999999999997</v>
       </c>
     </row>
-    <row r="721" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="721" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A721" s="2" t="s">
         <v>1314</v>
       </c>
@@ -27821,7 +27820,7 @@
         <v>54.994999999999997</v>
       </c>
     </row>
-    <row r="722" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="722" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A722" s="2" t="s">
         <v>1315</v>
       </c>
@@ -27853,7 +27852,7 @@
         <v>99.995000000000005</v>
       </c>
     </row>
-    <row r="723" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="723" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A723" s="2" t="s">
         <v>1316</v>
       </c>
@@ -27885,7 +27884,7 @@
         <v>99.995000000000005</v>
       </c>
     </row>
-    <row r="724" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="724" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A724" s="2" t="s">
         <v>1317</v>
       </c>
@@ -27917,7 +27916,7 @@
         <v>144.995</v>
       </c>
     </row>
-    <row r="725" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="725" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A725" s="2" t="s">
         <v>1318</v>
       </c>
@@ -27949,7 +27948,7 @@
         <v>144.995</v>
       </c>
     </row>
-    <row r="726" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="726" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A726" s="2" t="s">
         <v>1319</v>
       </c>
@@ -27981,7 +27980,7 @@
         <v>64.995000000000005</v>
       </c>
     </row>
-    <row r="727" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="727" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A727" s="2" t="s">
         <v>1320</v>
       </c>
@@ -28013,7 +28012,7 @@
         <v>64.995000000000005</v>
       </c>
     </row>
-    <row r="728" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="728" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A728" s="2" t="s">
         <v>1321</v>
       </c>
@@ -28045,7 +28044,7 @@
         <v>49.994999999999997</v>
       </c>
     </row>
-    <row r="729" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="729" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A729" s="2" t="s">
         <v>1322</v>
       </c>
@@ -28077,7 +28076,7 @@
         <v>49.994999999999997</v>
       </c>
     </row>
-    <row r="730" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="730" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A730" s="2" t="s">
         <v>1323</v>
       </c>
@@ -28109,7 +28108,7 @@
         <v>49.994999999999997</v>
       </c>
     </row>
-    <row r="731" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="731" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A731" s="2" t="s">
         <v>1324</v>
       </c>
@@ -28141,7 +28140,7 @@
         <v>49.994999999999997</v>
       </c>
     </row>
-    <row r="732" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="732" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A732" s="2" t="s">
         <v>1325</v>
       </c>
@@ -28173,7 +28172,7 @@
         <v>49.994999999999997</v>
       </c>
     </row>
-    <row r="733" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="733" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A733" s="2" t="s">
         <v>1326</v>
       </c>
@@ -28205,7 +28204,7 @@
         <v>54.994999999999997</v>
       </c>
     </row>
-    <row r="734" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="734" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A734" s="2" t="s">
         <v>1327</v>
       </c>
@@ -28237,7 +28236,7 @@
         <v>54.994999999999997</v>
       </c>
     </row>
-    <row r="735" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="735" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A735" s="2" t="s">
         <v>1328</v>
       </c>
@@ -28269,7 +28268,7 @@
         <v>54.994999999999997</v>
       </c>
     </row>
-    <row r="736" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="736" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A736" s="2" t="s">
         <v>1329</v>
       </c>
@@ -28301,7 +28300,7 @@
         <v>54.994999999999997</v>
       </c>
     </row>
-    <row r="737" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="737" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A737" s="2" t="s">
         <v>1330</v>
       </c>
@@ -28333,7 +28332,7 @@
         <v>44.994999999999997</v>
       </c>
     </row>
-    <row r="738" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="738" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A738" s="2" t="s">
         <v>1331</v>
       </c>
@@ -28365,7 +28364,7 @@
         <v>44.994999999999997</v>
       </c>
     </row>
-    <row r="739" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="739" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A739" s="2" t="s">
         <v>1332</v>
       </c>
@@ -28397,7 +28396,7 @@
         <v>44.994999999999997</v>
       </c>
     </row>
-    <row r="740" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="740" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A740" s="2" t="s">
         <v>1333</v>
       </c>
@@ -28429,7 +28428,7 @@
         <v>124.995</v>
       </c>
     </row>
-    <row r="741" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="741" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A741" s="2" t="s">
         <v>1334</v>
       </c>
@@ -28461,7 +28460,7 @@
         <v>124.995</v>
       </c>
     </row>
-    <row r="742" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="742" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A742" s="2" t="s">
         <v>1335</v>
       </c>
@@ -28493,7 +28492,7 @@
         <v>124.995</v>
       </c>
     </row>
-    <row r="743" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="743" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A743" s="2" t="s">
         <v>1336</v>
       </c>
@@ -28525,7 +28524,7 @@
         <v>99.995000000000005</v>
       </c>
     </row>
-    <row r="744" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="744" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A744" s="2" t="s">
         <v>1337</v>
       </c>
@@ -28557,7 +28556,7 @@
         <v>99.995000000000005</v>
       </c>
     </row>
-    <row r="745" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="745" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A745" s="2" t="s">
         <v>1338</v>
       </c>
@@ -28589,7 +28588,7 @@
         <v>99.995000000000005</v>
       </c>
     </row>
-    <row r="746" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="746" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A746" s="2" t="s">
         <v>1339</v>
       </c>
@@ -28621,7 +28620,7 @@
         <v>99.995000000000005</v>
       </c>
     </row>
-    <row r="747" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="747" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A747" s="2" t="s">
         <v>1340</v>
       </c>
@@ -28653,7 +28652,7 @@
         <v>99.995000000000005</v>
       </c>
     </row>
-    <row r="748" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="748" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A748" s="2" t="s">
         <v>1341</v>
       </c>
@@ -28685,7 +28684,7 @@
         <v>99.995000000000005</v>
       </c>
     </row>
-    <row r="749" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="749" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A749" s="2" t="s">
         <v>1342</v>
       </c>
@@ -28717,7 +28716,7 @@
         <v>89.995000000000005</v>
       </c>
     </row>
-    <row r="750" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="750" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A750" s="2" t="s">
         <v>1343</v>
       </c>
@@ -28749,7 +28748,7 @@
         <v>89.995000000000005</v>
       </c>
     </row>
-    <row r="751" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="751" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A751" s="2" t="s">
         <v>1344</v>
       </c>
@@ -28781,7 +28780,7 @@
         <v>89.995000000000005</v>
       </c>
     </row>
-    <row r="752" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="752" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A752" s="2" t="s">
         <v>1345</v>
       </c>
@@ -28813,7 +28812,7 @@
         <v>89.995000000000005</v>
       </c>
     </row>
-    <row r="753" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="753" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A753" s="2" t="s">
         <v>1346</v>
       </c>
@@ -28845,7 +28844,7 @@
         <v>89.995000000000005</v>
       </c>
     </row>
-    <row r="754" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="754" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A754" s="2" t="s">
         <v>1347</v>
       </c>
@@ -28877,7 +28876,7 @@
         <v>89.995000000000005</v>
       </c>
     </row>
-    <row r="755" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="755" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A755" s="2" t="s">
         <v>1348</v>
       </c>
@@ -28909,7 +28908,7 @@
         <v>99.995000000000005</v>
       </c>
     </row>
-    <row r="756" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="756" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A756" s="2" t="s">
         <v>1349</v>
       </c>
@@ -28941,7 +28940,7 @@
         <v>99.995000000000005</v>
       </c>
     </row>
-    <row r="757" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="757" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A757" s="2" t="s">
         <v>1350</v>
       </c>
@@ -28973,7 +28972,7 @@
         <v>99.995000000000005</v>
       </c>
     </row>
-    <row r="758" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="758" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A758" s="2" t="s">
         <v>1351</v>
       </c>
@@ -29005,7 +29004,7 @@
         <v>89.995000000000005</v>
       </c>
     </row>
-    <row r="759" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="759" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A759" s="2" t="s">
         <v>1352</v>
       </c>
@@ -29037,7 +29036,7 @@
         <v>89.995000000000005</v>
       </c>
     </row>
-    <row r="760" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="760" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A760" s="2" t="s">
         <v>1353</v>
       </c>
@@ -29069,7 +29068,7 @@
         <v>89.995000000000005</v>
       </c>
     </row>
-    <row r="761" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="761" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A761" s="2" t="s">
         <v>1354</v>
       </c>
@@ -29101,7 +29100,7 @@
         <v>94.995000000000005</v>
       </c>
     </row>
-    <row r="762" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="762" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A762" s="2" t="s">
         <v>1355</v>
       </c>
@@ -29133,7 +29132,7 @@
         <v>94.995000000000005</v>
       </c>
     </row>
-    <row r="763" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="763" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A763" s="2" t="s">
         <v>1356</v>
       </c>
@@ -29165,7 +29164,7 @@
         <v>94.995000000000005</v>
       </c>
     </row>
-    <row r="764" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="764" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A764" s="2" t="s">
         <v>1357</v>
       </c>
@@ -29197,7 +29196,7 @@
         <v>74.995000000000005</v>
       </c>
     </row>
-    <row r="765" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="765" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A765" s="2" t="s">
         <v>1358</v>
       </c>
@@ -29229,7 +29228,7 @@
         <v>74.995000000000005</v>
       </c>
     </row>
-    <row r="766" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="766" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A766" s="2" t="s">
         <v>1359</v>
       </c>
@@ -29261,7 +29260,7 @@
         <v>74.995000000000005</v>
       </c>
     </row>
-    <row r="767" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="767" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A767" s="2" t="s">
         <v>1360</v>
       </c>
@@ -29293,7 +29292,7 @@
         <v>74.995000000000005</v>
       </c>
     </row>
-    <row r="768" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="768" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A768" s="2" t="s">
         <v>1361</v>
       </c>
@@ -29325,7 +29324,7 @@
         <v>74.995000000000005</v>
       </c>
     </row>
-    <row r="769" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="769" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A769" s="2" t="s">
         <v>1362</v>
       </c>
@@ -29357,7 +29356,7 @@
         <v>74.995000000000005</v>
       </c>
     </row>
-    <row r="770" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="770" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A770" s="2" t="s">
         <v>1363</v>
       </c>
@@ -29389,7 +29388,7 @@
         <v>74.995000000000005</v>
       </c>
     </row>
-    <row r="771" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="771" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A771" s="2" t="s">
         <v>1364</v>
       </c>
@@ -29421,7 +29420,7 @@
         <v>74.995000000000005</v>
       </c>
     </row>
-    <row r="772" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="772" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A772" s="2" t="s">
         <v>1365</v>
       </c>
@@ -29453,7 +29452,7 @@
         <v>74.995000000000005</v>
       </c>
     </row>
-    <row r="773" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="773" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A773" s="2" t="s">
         <v>1366</v>
       </c>
@@ -29485,7 +29484,7 @@
         <v>64.995000000000005</v>
       </c>
     </row>
-    <row r="774" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="774" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A774" s="2" t="s">
         <v>1367</v>
       </c>
@@ -29517,7 +29516,7 @@
         <v>64.995000000000005</v>
       </c>
     </row>
-    <row r="775" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="775" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A775" s="2" t="s">
         <v>1368</v>
       </c>
@@ -29549,7 +29548,7 @@
         <v>64.995000000000005</v>
       </c>
     </row>
-    <row r="776" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="776" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A776" s="2" t="s">
         <v>1369</v>
       </c>
@@ -29581,7 +29580,7 @@
         <v>64.995000000000005</v>
       </c>
     </row>
-    <row r="777" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="777" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A777" s="2" t="s">
         <v>1370</v>
       </c>
@@ -29613,7 +29612,7 @@
         <v>64.995000000000005</v>
       </c>
     </row>
-    <row r="778" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="778" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A778" s="2" t="s">
         <v>1371</v>
       </c>
@@ -29645,7 +29644,7 @@
         <v>64.995000000000005</v>
       </c>
     </row>
-    <row r="779" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="779" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A779" s="2" t="s">
         <v>1372</v>
       </c>
@@ -29677,7 +29676,7 @@
         <v>64.995000000000005</v>
       </c>
     </row>
-    <row r="780" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="780" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A780" s="2" t="s">
         <v>1373</v>
       </c>
@@ -29709,7 +29708,7 @@
         <v>64.995000000000005</v>
       </c>
     </row>
-    <row r="781" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="781" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A781" s="2" t="s">
         <v>1374</v>
       </c>
@@ -29741,7 +29740,7 @@
         <v>64.995000000000005</v>
       </c>
     </row>
-    <row r="782" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="782" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A782" s="2" t="s">
         <v>1375</v>
       </c>
@@ -29773,7 +29772,7 @@
         <v>59.994999999999997</v>
       </c>
     </row>
-    <row r="783" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="783" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A783" s="2" t="s">
         <v>1376</v>
       </c>
@@ -29805,7 +29804,7 @@
         <v>59.994999999999997</v>
       </c>
     </row>
-    <row r="784" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="784" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A784" s="2" t="s">
         <v>1377</v>
       </c>
@@ -29837,7 +29836,7 @@
         <v>59.994999999999997</v>
       </c>
     </row>
-    <row r="785" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="785" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A785" s="2" t="s">
         <v>1378</v>
       </c>
@@ -29869,7 +29868,7 @@
         <v>59.994999999999997</v>
       </c>
     </row>
-    <row r="786" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="786" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A786" s="2" t="s">
         <v>1379</v>
       </c>
@@ -29901,7 +29900,7 @@
         <v>59.994999999999997</v>
       </c>
     </row>
-    <row r="787" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="787" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A787" s="2" t="s">
         <v>1380</v>
       </c>
@@ -29933,7 +29932,7 @@
         <v>59.994999999999997</v>
       </c>
     </row>
-    <row r="788" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="788" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A788" s="2" t="s">
         <v>1381</v>
       </c>
@@ -29965,7 +29964,7 @@
         <v>59.994999999999997</v>
       </c>
     </row>
-    <row r="789" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="789" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A789" s="2" t="s">
         <v>1382</v>
       </c>
@@ -29997,7 +29996,7 @@
         <v>59.994999999999997</v>
       </c>
     </row>
-    <row r="790" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="790" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A790" s="2" t="s">
         <v>1383</v>
       </c>
@@ -30029,7 +30028,7 @@
         <v>59.994999999999997</v>
       </c>
     </row>
-    <row r="791" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="791" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A791" s="2" t="s">
         <v>1384</v>
       </c>
@@ -30061,7 +30060,7 @@
         <v>44.994999999999997</v>
       </c>
     </row>
-    <row r="792" spans="1:10" s="2" customFormat="1" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="792" spans="1:10" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A792" s="2" t="s">
         <v>1385</v>
       </c>
@@ -30093,7 +30092,7 @@
         <v>44.994999999999997</v>
       </c>
     </row>
-    <row r="793" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="793" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A793" s="1" t="s">
         <v>1404</v>
       </c>
@@ -30125,7 +30124,7 @@
         <v>274.995</v>
       </c>
     </row>
-    <row r="794" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="794" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A794" s="1" t="s">
         <v>1406</v>
       </c>
@@ -30157,7 +30156,7 @@
         <v>274.995</v>
       </c>
     </row>
-    <row r="795" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="795" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A795" s="1" t="s">
         <v>1407</v>
       </c>
@@ -30189,7 +30188,7 @@
         <v>274.995</v>
       </c>
     </row>
-    <row r="796" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="796" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A796" s="1" t="s">
         <v>1408</v>
       </c>
@@ -30221,7 +30220,7 @@
         <v>274.995</v>
       </c>
     </row>
-    <row r="797" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="797" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A797" s="1" t="s">
         <v>1409</v>
       </c>
@@ -30253,7 +30252,7 @@
         <v>399.995</v>
       </c>
     </row>
-    <row r="798" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="798" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A798" s="1" t="s">
         <v>1410</v>
       </c>
@@ -30285,7 +30284,7 @@
         <v>349.995</v>
       </c>
     </row>
-    <row r="799" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="799" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A799" s="1" t="s">
         <v>1411</v>
       </c>
@@ -30317,7 +30316,7 @@
         <v>299.995</v>
       </c>
     </row>
-    <row r="800" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="800" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A800" s="1" t="s">
         <v>1413</v>
       </c>
@@ -30349,7 +30348,7 @@
         <v>299.995</v>
       </c>
     </row>
-    <row r="801" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="801" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A801" s="1" t="s">
         <v>1414</v>
       </c>
@@ -30381,7 +30380,7 @@
         <v>274.995</v>
       </c>
     </row>
-    <row r="802" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="802" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A802" s="1" t="s">
         <v>1416</v>
       </c>
@@ -30413,7 +30412,7 @@
         <v>274.995</v>
       </c>
     </row>
-    <row r="803" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="803" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A803" s="1" t="s">
         <v>1417</v>
       </c>
@@ -30445,7 +30444,7 @@
         <v>249.995</v>
       </c>
     </row>
-    <row r="804" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="804" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A804" s="1" t="s">
         <v>1419</v>
       </c>
@@ -30477,7 +30476,7 @@
         <v>249.995</v>
       </c>
     </row>
-    <row r="805" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="805" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A805" s="1" t="s">
         <v>1420</v>
       </c>
@@ -30509,7 +30508,7 @@
         <v>249.995</v>
       </c>
     </row>
-    <row r="806" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="806" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A806" s="1" t="s">
         <v>1421</v>
       </c>
@@ -30541,7 +30540,7 @@
         <v>249.995</v>
       </c>
     </row>
-    <row r="807" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="807" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A807" s="1" t="s">
         <v>1422</v>
       </c>
@@ -30573,7 +30572,7 @@
         <v>249.995</v>
       </c>
     </row>
-    <row r="808" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="808" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A808" s="1" t="s">
         <v>1423</v>
       </c>
@@ -30606,13 +30605,7 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:J808" xr:uid="{3A91E150-05DE-47E3-9A71-EF43C5F49301}">
-    <filterColumn colId="4">
-      <filters>
-        <filter val="VOA 3"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
+  <autoFilter ref="A1:J808" xr:uid="{3A91E150-05DE-47E3-9A71-EF43C5F49301}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait"/>
   <headerFooter alignWithMargins="0"/>
